--- a/University-Projects/UvA/Event-Projects/M&A Finance Accelerator 28.02 v35m.xlsx
+++ b/University-Projects/UvA/Event-Projects/M&A Finance Accelerator 28.02 v35m.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amsuni-my.sharepoint.com/personal/theodor_hogan_student_uva_nl/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\theod\OneDrive\Documents\GitHub\finance-models\University-Projects\UvA\Event-Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{EEE73642-A1E1-4379-8910-0C31FE12F51C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{514F25FE-4A8B-45BD-B3CA-13A0F71D6875}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73886C49-0544-47B5-8DF8-EFC25E98C821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" activeTab="1" xr2:uid="{5F141CAC-DE77-4535-A101-6F03B64064EC}"/>
+    <workbookView minimized="1" xWindow="32810" yWindow="18490" windowWidth="5590" windowHeight="2390" firstSheet="1" activeTab="1" xr2:uid="{5F141CAC-DE77-4535-A101-6F03B64064EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="2" r:id="rId1"/>
@@ -49,7 +49,7 @@
     <definedName name="IQ_YTD">3000</definedName>
     <definedName name="IQ_YTDMONTH" hidden="1">130000</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1301,6 +1301,7 @@
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="13">
@@ -4522,18 +4523,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB54DB0E-BBE9-4CFE-B6E1-F1809739DF2A}">
   <dimension ref="B1:XX1000"/>
-  <sheetFormatPr defaultColWidth="12" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="12" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.265625" style="289" customWidth="1"/>
+    <col min="1" max="1" width="4.26953125" style="289" customWidth="1"/>
     <col min="2" max="2" width="12" style="289"/>
-    <col min="3" max="3" width="32.59765625" style="289" customWidth="1"/>
+    <col min="3" max="3" width="32.6328125" style="289" customWidth="1"/>
     <col min="4" max="4" width="12" style="289"/>
-    <col min="5" max="5" width="63.3984375" style="289" customWidth="1"/>
+    <col min="5" max="5" width="63.36328125" style="289" customWidth="1"/>
     <col min="6" max="16384" width="12" style="289"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B2" s="290"/>
       <c r="C2" s="291"/>
       <c r="D2" s="291"/>
@@ -4541,23 +4542,23 @@
       <c r="F2" s="291"/>
       <c r="G2" s="292"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B3" s="293"/>
       <c r="G3" s="294"/>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B4" s="293"/>
       <c r="G4" s="294"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B5" s="293"/>
       <c r="G5" s="294"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B6" s="293"/>
       <c r="G6" s="294"/>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="293"/>
       <c r="C7" s="295" t="s">
         <v>205</v>
@@ -4565,7 +4566,7 @@
       <c r="D7" s="296"/>
       <c r="G7" s="294"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="293"/>
       <c r="C8" s="297" t="s">
         <v>206</v>
@@ -4575,7 +4576,7 @@
       </c>
       <c r="G8" s="294"/>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="293"/>
       <c r="C9" s="297" t="s">
         <v>208</v>
@@ -4585,7 +4586,7 @@
       </c>
       <c r="G9" s="294"/>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="293"/>
       <c r="C10" s="297" t="s">
         <v>210</v>
@@ -4593,7 +4594,7 @@
       <c r="D10" s="300"/>
       <c r="G10" s="294"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="293"/>
       <c r="C11" s="297" t="s">
         <v>211</v>
@@ -4603,7 +4604,7 @@
       </c>
       <c r="G11" s="294"/>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="293"/>
       <c r="C12" s="302" t="s">
         <v>213</v>
@@ -4613,18 +4614,18 @@
       </c>
       <c r="G12" s="294"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="293"/>
       <c r="G13" s="294"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="293"/>
       <c r="C14" s="303" t="s">
         <v>214</v>
       </c>
       <c r="G14" s="294"/>
     </row>
-    <row r="15" spans="2:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="293"/>
       <c r="C15" s="407" t="s">
         <v>215</v>
@@ -4634,7 +4635,7 @@
       <c r="F15" s="409"/>
       <c r="G15" s="294"/>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="293"/>
       <c r="C16" s="410"/>
       <c r="D16" s="411"/>
@@ -4642,7 +4643,7 @@
       <c r="F16" s="412"/>
       <c r="G16" s="294"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="293"/>
       <c r="C17" s="410"/>
       <c r="D17" s="411"/>
@@ -4650,7 +4651,7 @@
       <c r="F17" s="412"/>
       <c r="G17" s="294"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B18" s="293"/>
       <c r="C18" s="410"/>
       <c r="D18" s="411"/>
@@ -4658,7 +4659,7 @@
       <c r="F18" s="412"/>
       <c r="G18" s="294"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B19" s="293"/>
       <c r="C19" s="410"/>
       <c r="D19" s="411"/>
@@ -4666,7 +4667,7 @@
       <c r="F19" s="412"/>
       <c r="G19" s="294"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B20" s="293"/>
       <c r="C20" s="410"/>
       <c r="D20" s="411"/>
@@ -4674,7 +4675,7 @@
       <c r="F20" s="412"/>
       <c r="G20" s="294"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B21" s="293"/>
       <c r="C21" s="410"/>
       <c r="D21" s="411"/>
@@ -4682,7 +4683,7 @@
       <c r="F21" s="412"/>
       <c r="G21" s="294"/>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B22" s="293"/>
       <c r="C22" s="410"/>
       <c r="D22" s="411"/>
@@ -4690,7 +4691,7 @@
       <c r="F22" s="412"/>
       <c r="G22" s="294"/>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B23" s="293"/>
       <c r="C23" s="410"/>
       <c r="D23" s="411"/>
@@ -4698,7 +4699,7 @@
       <c r="F23" s="412"/>
       <c r="G23" s="294"/>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B24" s="293"/>
       <c r="C24" s="410"/>
       <c r="D24" s="411"/>
@@ -4706,7 +4707,7 @@
       <c r="F24" s="412"/>
       <c r="G24" s="294"/>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="293"/>
       <c r="C25" s="413"/>
       <c r="D25" s="414"/>
@@ -4714,7 +4715,7 @@
       <c r="F25" s="415"/>
       <c r="G25" s="294"/>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="293"/>
       <c r="C26" s="303"/>
       <c r="D26" s="416"/>
@@ -4722,7 +4723,7 @@
       <c r="F26" s="416"/>
       <c r="G26" s="294"/>
     </row>
-    <row r="27" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="27" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B27" s="304"/>
       <c r="C27" s="305"/>
       <c r="D27" s="417"/>
@@ -4730,7 +4731,7 @@
       <c r="F27" s="417"/>
       <c r="G27" s="306"/>
     </row>
-    <row r="1000" spans="648:648" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="1000" spans="648:648" ht="15.5" x14ac:dyDescent="0.35">
       <c r="XX1000" s="406">
         <v>102911</v>
       </c>
@@ -4768,21 +4769,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD7048BE-57EC-43E7-9BCB-957354E27671}">
   <dimension ref="B4:XX1000"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="1"/>
-    <col min="2" max="2" width="9.1328125" style="34"/>
-    <col min="3" max="3" width="3.73046875" style="1" customWidth="1"/>
-    <col min="4" max="7" width="13.73046875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="5.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="17" width="13.59765625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="1.73046875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="7.73046875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="16.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.1328125" style="1"/>
+    <col min="1" max="1" width="9.08984375" style="1"/>
+    <col min="2" max="2" width="9.08984375" style="34"/>
+    <col min="3" max="3" width="3.7265625" style="1" customWidth="1"/>
+    <col min="4" max="7" width="13.7265625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="5.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="17" width="13.6328125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="1.7265625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7.7265625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="16.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:23" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="D4" s="2" t="s">
         <v>0</v>
       </c>
@@ -4791,7 +4792,7 @@
       <c r="G4" s="4"/>
       <c r="U4"/>
     </row>
-    <row r="5" spans="2:23" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:23" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="D5" s="5" t="s">
         <v>1</v>
       </c>
@@ -4811,14 +4812,14 @@
       <c r="R5" s="8"/>
       <c r="S5" s="8"/>
     </row>
-    <row r="7" spans="2:23" s="311" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:23" s="311" customFormat="1" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="310"/>
       <c r="D7" s="314"/>
       <c r="E7" s="312"/>
       <c r="F7" s="312"/>
       <c r="G7" s="313"/>
     </row>
-    <row r="9" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B9" s="307"/>
       <c r="C9" s="9"/>
       <c r="D9" s="10" t="s">
@@ -4845,7 +4846,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D10" s="17" t="s">
         <v>7</v>
       </c>
@@ -4895,10 +4896,10 @@
         <v>2022 - 2027</v>
       </c>
     </row>
-    <row r="11" spans="2:23" ht="3.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:23" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H11" s="26"/>
     </row>
-    <row r="12" spans="2:23" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D12" s="1" t="s">
         <v>9</v>
       </c>
@@ -4942,7 +4943,7 @@
         <v>0.12486109052905014</v>
       </c>
     </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D13" s="29" t="s">
         <v>11</v>
       </c>
@@ -4989,7 +4990,7 @@
       </c>
       <c r="W13" s="419"/>
     </row>
-    <row r="14" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D14" s="31" t="s">
         <v>12</v>
       </c>
@@ -5037,7 +5038,7 @@
       <c r="V14" s="420"/>
       <c r="W14" s="421"/>
     </row>
-    <row r="15" spans="2:23" ht="6.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:23" ht="6.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D15" s="34"/>
       <c r="E15" s="34"/>
       <c r="F15" s="34"/>
@@ -5057,7 +5058,7 @@
       <c r="V15" s="420"/>
       <c r="W15" s="421"/>
     </row>
-    <row r="16" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D16" s="29" t="s">
         <v>13</v>
       </c>
@@ -5104,7 +5105,7 @@
       <c r="V16" s="420"/>
       <c r="W16" s="421"/>
     </row>
-    <row r="17" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D17" s="29" t="s">
         <v>14</v>
       </c>
@@ -5151,7 +5152,7 @@
       <c r="V17" s="420"/>
       <c r="W17" s="421"/>
     </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D18" s="39" t="s">
         <v>15</v>
       </c>
@@ -5198,7 +5199,7 @@
       <c r="V18" s="420"/>
       <c r="W18" s="421"/>
     </row>
-    <row r="19" spans="2:23" ht="6.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:23" ht="6.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D19" s="34"/>
       <c r="E19" s="34"/>
       <c r="F19" s="34"/>
@@ -5218,7 +5219,7 @@
       <c r="V19" s="420"/>
       <c r="W19" s="421"/>
     </row>
-    <row r="20" spans="2:23" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="20" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D20" s="29" t="s">
         <v>16</v>
       </c>
@@ -5260,7 +5261,7 @@
       <c r="V20" s="422"/>
       <c r="W20" s="423"/>
     </row>
-    <row r="21" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D21" s="29" t="s">
         <v>17</v>
       </c>
@@ -5305,7 +5306,7 @@
       <c r="S21" s="34"/>
       <c r="T21" s="34"/>
     </row>
-    <row r="22" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D22" s="40" t="s">
         <v>18</v>
       </c>
@@ -5350,7 +5351,7 @@
       <c r="S22" s="34"/>
       <c r="T22" s="34"/>
     </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D23" s="29" t="s">
         <v>19</v>
       </c>
@@ -5395,7 +5396,7 @@
       <c r="S23" s="34"/>
       <c r="T23" s="34"/>
     </row>
-    <row r="24" spans="2:23" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="24" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D24" s="41" t="s">
         <v>20</v>
       </c>
@@ -5440,12 +5441,12 @@
       <c r="S24" s="34"/>
       <c r="T24" s="34"/>
     </row>
-    <row r="25" spans="2:23" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:23" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="L25" s="44"/>
       <c r="S25" s="34"/>
       <c r="T25" s="34"/>
     </row>
-    <row r="26" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D26" s="1" t="s">
         <v>21</v>
       </c>
@@ -5487,7 +5488,7 @@
       <c r="S26" s="34"/>
       <c r="T26" s="34"/>
     </row>
-    <row r="27" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D27" s="29" t="s">
         <v>22</v>
       </c>
@@ -5529,7 +5530,7 @@
       <c r="S27" s="34"/>
       <c r="T27" s="34"/>
     </row>
-    <row r="28" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D28" s="47" t="s">
         <v>23</v>
       </c>
@@ -5575,7 +5576,7 @@
       <c r="S28" s="34"/>
       <c r="T28" s="34"/>
     </row>
-    <row r="29" spans="2:23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B29" s="308" t="s">
         <v>24</v>
       </c>
@@ -5588,7 +5589,7 @@
       <c r="T29" s="1"/>
       <c r="U29" s="1"/>
     </row>
-    <row r="30" spans="2:23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B30" s="34"/>
       <c r="C30" s="1"/>
       <c r="D30" s="51" t="s">
@@ -5604,7 +5605,7 @@
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
     </row>
-    <row r="31" spans="2:23" ht="3.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:23" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H31" s="26"/>
       <c r="L31" s="52">
         <v>0</v>
@@ -5613,7 +5614,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D32" s="53" t="s">
         <v>27</v>
       </c>
@@ -5657,7 +5658,7 @@
         <v>-1.2499999999999997E-2</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D33" s="53" t="s">
         <v>29</v>
       </c>
@@ -5703,7 +5704,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D34" s="53" t="s">
         <v>30</v>
       </c>
@@ -5749,7 +5750,7 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D35" s="53" t="s">
         <v>31</v>
       </c>
@@ -5795,7 +5796,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="36" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D36" s="53" t="s">
         <v>32</v>
       </c>
@@ -5841,7 +5842,7 @@
         <v>-5.4906935372091899E-4</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D37" s="53" t="s">
         <v>33</v>
       </c>
@@ -5884,7 +5885,7 @@
       <c r="R37" s="59"/>
       <c r="S37" s="65"/>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D38" s="53" t="s">
         <v>34</v>
       </c>
@@ -5929,7 +5930,7 @@
       <c r="R38" s="59"/>
       <c r="S38" s="59"/>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D39" s="53" t="s">
         <v>35</v>
       </c>
@@ -5973,7 +5974,7 @@
       <c r="R39" s="59"/>
       <c r="S39" s="59"/>
     </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D40" s="53"/>
       <c r="E40" s="53"/>
       <c r="F40" s="53"/>
@@ -5992,7 +5993,7 @@
       <c r="S40" s="59"/>
       <c r="U40" s="368"/>
     </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D41" s="53"/>
       <c r="E41" s="53"/>
       <c r="F41" s="53"/>
@@ -6010,7 +6011,7 @@
       <c r="R41" s="59"/>
       <c r="S41" s="59"/>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D42" s="53"/>
       <c r="E42" s="53"/>
       <c r="F42" s="53"/>
@@ -6028,7 +6029,7 @@
       <c r="R42" s="59"/>
       <c r="S42" s="59"/>
     </row>
-    <row r="44" spans="2:21" s="311" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="2:21" s="311" customFormat="1" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B44" s="310" t="s">
         <v>2</v>
       </c>
@@ -6039,7 +6040,7 @@
       <c r="F44" s="312"/>
       <c r="G44" s="313"/>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B46" s="307"/>
       <c r="C46" s="9"/>
       <c r="D46" s="10" t="s">
@@ -6063,7 +6064,7 @@
       <c r="P46" s="15"/>
       <c r="Q46" s="15"/>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D47" s="17" t="s">
         <v>7</v>
       </c>
@@ -6106,7 +6107,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="48" spans="2:21" ht="3.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:21" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B48" s="307"/>
       <c r="C48" s="9"/>
       <c r="D48" s="18"/>
@@ -6124,7 +6125,7 @@
       <c r="P48" s="70"/>
       <c r="Q48" s="70"/>
     </row>
-    <row r="49" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="49" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D49" s="71" t="s">
         <v>38</v>
       </c>
@@ -6167,7 +6168,7 @@
         <v>17391.407041119543</v>
       </c>
     </row>
-    <row r="50" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="50" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D50" s="71" t="s">
         <v>39</v>
       </c>
@@ -6210,7 +6211,7 @@
         <v>4932</v>
       </c>
     </row>
-    <row r="51" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="51" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D51" s="71" t="s">
         <v>40</v>
       </c>
@@ -6253,7 +6254,7 @@
         <v>2434.8081120644533</v>
       </c>
     </row>
-    <row r="52" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="52" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D52" s="71" t="s">
         <v>41</v>
       </c>
@@ -6296,7 +6297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="53" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D53" s="71" t="s">
         <v>42</v>
       </c>
@@ -6339,7 +6340,7 @@
         <v>2956.5527075068362</v>
       </c>
     </row>
-    <row r="54" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="54" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D54" s="73" t="s">
         <v>43</v>
       </c>
@@ -6382,7 +6383,7 @@
         <v>27714.76786069083</v>
       </c>
     </row>
-    <row r="55" spans="4:26" ht="6.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="55" spans="4:26" ht="6.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D55" s="76"/>
       <c r="E55" s="76"/>
       <c r="F55" s="76"/>
@@ -6398,7 +6399,7 @@
       <c r="P55" s="77"/>
       <c r="Q55" s="77"/>
     </row>
-    <row r="56" spans="4:26" ht="14.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="4:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D56" s="71" t="s">
         <v>44</v>
       </c>
@@ -6449,7 +6450,7 @@
       <c r="Y56" s="436"/>
       <c r="Z56" s="419"/>
     </row>
-    <row r="57" spans="4:26" ht="14.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="4:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D57" s="71" t="s">
         <v>45</v>
       </c>
@@ -6493,7 +6494,7 @@
       <c r="Y57" s="437"/>
       <c r="Z57" s="421"/>
     </row>
-    <row r="58" spans="4:26" ht="14.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="4:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D58" s="71" t="s">
         <v>46</v>
       </c>
@@ -6537,7 +6538,7 @@
       <c r="Y58" s="437"/>
       <c r="Z58" s="421"/>
     </row>
-    <row r="59" spans="4:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="59" spans="4:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D59" s="79" t="s">
         <v>47</v>
       </c>
@@ -6586,7 +6587,7 @@
       <c r="Y59" s="437"/>
       <c r="Z59" s="421"/>
     </row>
-    <row r="60" spans="4:26" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="4:26" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="D60" s="83"/>
       <c r="E60" s="83"/>
       <c r="F60" s="83"/>
@@ -6608,7 +6609,7 @@
       <c r="Y60" s="437"/>
       <c r="Z60" s="421"/>
     </row>
-    <row r="61" spans="4:26" ht="14.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="4:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D61" s="84" t="s">
         <v>48</v>
       </c>
@@ -6657,7 +6658,7 @@
       <c r="Y61" s="437"/>
       <c r="Z61" s="421"/>
     </row>
-    <row r="62" spans="4:26" ht="14.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="4:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D62" s="84" t="s">
         <v>49</v>
       </c>
@@ -6706,7 +6707,7 @@
       <c r="Y62" s="437"/>
       <c r="Z62" s="421"/>
     </row>
-    <row r="63" spans="4:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="63" spans="4:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D63" s="85" t="s">
         <v>50</v>
       </c>
@@ -6755,7 +6756,7 @@
       <c r="Y63" s="438"/>
       <c r="Z63" s="423"/>
     </row>
-    <row r="64" spans="4:26" ht="6.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="4:26" ht="6.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D64" s="87"/>
       <c r="E64" s="87"/>
       <c r="F64" s="87"/>
@@ -6771,7 +6772,7 @@
       <c r="P64" s="77"/>
       <c r="Q64" s="77"/>
     </row>
-    <row r="65" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="65" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D65" s="84" t="s">
         <v>51</v>
       </c>
@@ -6817,7 +6818,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="66" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="66" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D66" s="84" t="s">
         <v>52</v>
       </c>
@@ -6853,7 +6854,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="67" spans="4:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="67" spans="4:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D67" s="359" t="s">
         <v>53</v>
       </c>
@@ -6896,7 +6897,7 @@
         <v>6669.8324117919838</v>
       </c>
     </row>
-    <row r="68" spans="4:21" ht="6.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="4:21" ht="6.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="D68" s="89"/>
       <c r="E68" s="89"/>
       <c r="F68" s="89"/>
@@ -6912,7 +6913,7 @@
       <c r="P68" s="91"/>
       <c r="Q68" s="91"/>
     </row>
-    <row r="69" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="69" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D69" s="87" t="s">
         <v>54</v>
       </c>
@@ -6955,7 +6956,7 @@
         <v>33299.105966742231</v>
       </c>
     </row>
-    <row r="70" spans="4:21" ht="6.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="4:21" ht="6.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D70" s="87"/>
       <c r="E70" s="87"/>
       <c r="F70" s="87"/>
@@ -6971,7 +6972,7 @@
       <c r="P70" s="90"/>
       <c r="Q70" s="90"/>
     </row>
-    <row r="71" spans="4:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="71" spans="4:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D71" s="79" t="s">
         <v>55</v>
       </c>
@@ -7014,7 +7015,7 @@
         <v>39968.938378534214</v>
       </c>
     </row>
-    <row r="72" spans="4:21" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="4:21" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="D72" s="92" t="s">
         <v>56</v>
       </c>
@@ -7056,7 +7057,7 @@
       </c>
       <c r="R72" s="201"/>
     </row>
-    <row r="73" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="73" spans="4:21" x14ac:dyDescent="0.35">
       <c r="H73" s="26"/>
       <c r="I73" s="94"/>
       <c r="J73" s="94"/>
@@ -7068,7 +7069,7 @@
       <c r="P73" s="94"/>
       <c r="Q73" s="94"/>
     </row>
-    <row r="74" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="74" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D74" s="51" t="s">
         <v>57</v>
       </c>
@@ -7088,7 +7089,7 @@
       <c r="P74"/>
       <c r="Q74"/>
     </row>
-    <row r="75" spans="4:21" ht="3.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="4:21" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H75" s="26"/>
       <c r="L75" s="52">
         <v>0</v>
@@ -7097,7 +7098,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="76" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="76" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D76" s="97" t="s">
         <v>58</v>
       </c>
@@ -7139,7 +7140,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="77" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="77" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D77" s="97" t="s">
         <v>59</v>
       </c>
@@ -7182,7 +7183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="78" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D78" s="97" t="s">
         <v>60</v>
       </c>
@@ -7224,7 +7225,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="79" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="79" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D79" s="102" t="s">
         <v>61</v>
       </c>
@@ -7266,7 +7267,7 @@
         <v>234.90263671875005</v>
       </c>
     </row>
-    <row r="80" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="80" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D80" s="102" t="s">
         <v>62</v>
       </c>
@@ -7307,7 +7308,7 @@
         <v>1.3506760133446791E-2</v>
       </c>
     </row>
-    <row r="81" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D81" s="110" t="s">
         <v>63</v>
       </c>
@@ -7349,7 +7350,7 @@
         <v>0.124</v>
       </c>
     </row>
-    <row r="82" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D82" s="97" t="s">
         <v>64</v>
       </c>
@@ -7391,7 +7392,7 @@
         <v>0.39800000000000002</v>
       </c>
     </row>
-    <row r="83" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D83" s="110" t="s">
         <v>65</v>
       </c>
@@ -7421,7 +7422,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="84" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D84" s="110"/>
       <c r="E84" s="110"/>
       <c r="F84" s="110"/>
@@ -7437,7 +7438,7 @@
       <c r="P84" s="105"/>
       <c r="Q84" s="105"/>
     </row>
-    <row r="85" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D85" s="110"/>
       <c r="E85" s="110"/>
       <c r="F85" s="110"/>
@@ -7453,7 +7454,7 @@
       <c r="P85" s="105"/>
       <c r="Q85" s="105"/>
     </row>
-    <row r="86" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D86" s="110"/>
       <c r="E86" s="110"/>
       <c r="F86" s="110"/>
@@ -7469,10 +7470,10 @@
       <c r="P86" s="105"/>
       <c r="Q86" s="105"/>
     </row>
-    <row r="87" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:17" x14ac:dyDescent="0.35">
       <c r="H87" s="26"/>
     </row>
-    <row r="88" spans="2:17" s="311" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="2:17" s="311" customFormat="1" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B88" s="310" t="s">
         <v>36</v>
       </c>
@@ -7483,10 +7484,10 @@
       <c r="F88" s="312"/>
       <c r="G88" s="313"/>
     </row>
-    <row r="89" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:17" x14ac:dyDescent="0.35">
       <c r="H89" s="26"/>
     </row>
-    <row r="90" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B90" s="307"/>
       <c r="C90" s="9"/>
       <c r="D90" s="10" t="s">
@@ -7510,7 +7511,7 @@
       <c r="P90" s="15"/>
       <c r="Q90" s="15"/>
     </row>
-    <row r="91" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D91" s="17" t="s">
         <v>7</v>
       </c>
@@ -7553,10 +7554,10 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="92" spans="2:17" ht="3.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:17" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H92" s="26"/>
     </row>
-    <row r="93" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D93" s="113" t="s">
         <v>68</v>
       </c>
@@ -7599,7 +7600,7 @@
         <v>4578.5087084312108</v>
       </c>
     </row>
-    <row r="94" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D94" s="116" t="s">
         <v>22</v>
       </c>
@@ -7642,7 +7643,7 @@
         <v>379.19914731031537</v>
       </c>
     </row>
-    <row r="95" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D95" s="116" t="s">
         <v>70</v>
       </c>
@@ -7685,7 +7686,7 @@
         <v>597.3158754194842</v>
       </c>
     </row>
-    <row r="96" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D96" s="118" t="s">
         <v>71</v>
       </c>
@@ -7727,7 +7728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="97" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D97" s="119" t="s">
         <v>72</v>
       </c>
@@ -7745,7 +7746,7 @@
       <c r="P97" s="114"/>
       <c r="Q97" s="114"/>
     </row>
-    <row r="98" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="98" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D98" s="120" t="s">
         <v>73</v>
       </c>
@@ -7788,7 +7789,7 @@
         <v>-221.34619200585939</v>
       </c>
     </row>
-    <row r="99" spans="4:26" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="99" spans="4:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D99" s="120" t="s">
         <v>41</v>
       </c>
@@ -7831,7 +7832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="100" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D100" s="120" t="s">
         <v>42</v>
       </c>
@@ -7882,7 +7883,7 @@
       <c r="Y100" s="436"/>
       <c r="Z100" s="419"/>
     </row>
-    <row r="101" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="101" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D101" s="120" t="s">
         <v>48</v>
       </c>
@@ -7931,7 +7932,7 @@
       <c r="Y101" s="437"/>
       <c r="Z101" s="421"/>
     </row>
-    <row r="102" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="102" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D102" s="120" t="s">
         <v>49</v>
       </c>
@@ -7980,7 +7981,7 @@
       <c r="Y102" s="437"/>
       <c r="Z102" s="421"/>
     </row>
-    <row r="103" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="103" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D103" s="120" t="s">
         <v>74</v>
       </c>
@@ -8022,7 +8023,7 @@
       <c r="Y103" s="437"/>
       <c r="Z103" s="421"/>
     </row>
-    <row r="104" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="104" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D104" s="121" t="s">
         <v>75</v>
       </c>
@@ -8071,7 +8072,7 @@
       <c r="Y104" s="437"/>
       <c r="Z104" s="421"/>
     </row>
-    <row r="105" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="105" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D105" s="125"/>
       <c r="E105" s="125"/>
       <c r="F105" s="125"/>
@@ -8093,7 +8094,7 @@
       <c r="Y105" s="437"/>
       <c r="Z105" s="421"/>
     </row>
-    <row r="106" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="106" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D106" s="118" t="s">
         <v>61</v>
       </c>
@@ -8142,7 +8143,7 @@
       <c r="Y106" s="437"/>
       <c r="Z106" s="421"/>
     </row>
-    <row r="107" spans="4:26" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="107" spans="4:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D107" s="118" t="s">
         <v>76</v>
       </c>
@@ -8190,7 +8191,7 @@
       <c r="Y107" s="438"/>
       <c r="Z107" s="423"/>
     </row>
-    <row r="108" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="108" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D108" s="118" t="s">
         <v>77</v>
       </c>
@@ -8236,7 +8237,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="109" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="109" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D109" s="126" t="s">
         <v>78</v>
       </c>
@@ -8279,7 +8280,7 @@
         <v>-234.90263671875005</v>
       </c>
     </row>
-    <row r="110" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="110" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D110" s="125"/>
       <c r="E110" s="125"/>
       <c r="F110" s="125"/>
@@ -8295,7 +8296,7 @@
       <c r="P110" s="114"/>
       <c r="Q110" s="114"/>
     </row>
-    <row r="111" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="111" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D111" s="118" t="s">
         <v>79</v>
       </c>
@@ -8333,7 +8334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="112" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D112" s="118" t="s">
         <v>80</v>
       </c>
@@ -8376,7 +8377,7 @@
         <v>-400</v>
       </c>
     </row>
-    <row r="113" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="113" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D113" s="118" t="s">
         <v>81</v>
       </c>
@@ -8418,7 +8419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="114" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D114" s="118" t="s">
         <v>82</v>
       </c>
@@ -8461,7 +8462,7 @@
         <v>-1144.6271771078027</v>
       </c>
     </row>
-    <row r="115" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="115" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D115" s="118" t="s">
         <v>71</v>
       </c>
@@ -8497,7 +8498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="116" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D116" s="121" t="s">
         <v>83</v>
       </c>
@@ -8540,7 +8541,7 @@
         <v>-1544.6271771078027</v>
       </c>
     </row>
-    <row r="117" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="117" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D117" s="125"/>
       <c r="E117" s="125"/>
       <c r="F117" s="125"/>
@@ -8556,7 +8557,7 @@
       <c r="P117" s="114"/>
       <c r="Q117" s="114"/>
     </row>
-    <row r="118" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="118" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D118" s="128" t="s">
         <v>84</v>
       </c>
@@ -8592,7 +8593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="119" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D119" s="129" t="s">
         <v>85</v>
       </c>
@@ -8635,7 +8636,7 @@
         <v>3320.6591136469888</v>
       </c>
     </row>
-    <row r="120" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="120" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D120" s="118" t="s">
         <v>86</v>
       </c>
@@ -8678,7 +8679,7 @@
         <v>14070.747927472552</v>
       </c>
     </row>
-    <row r="121" spans="4:19" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="121" spans="4:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D121" s="133" t="s">
         <v>87</v>
       </c>
@@ -8721,10 +8722,10 @@
         <v>17391.407041119543</v>
       </c>
     </row>
-    <row r="122" spans="4:19" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="4:19" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="L122" s="44"/>
     </row>
-    <row r="123" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="123" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D123" s="51" t="s">
         <v>88</v>
       </c>
@@ -8744,7 +8745,7 @@
       <c r="P123"/>
       <c r="Q123"/>
     </row>
-    <row r="124" spans="4:19" ht="3.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="4:19" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H124" s="26"/>
       <c r="L124" s="52">
         <v>0</v>
@@ -8753,7 +8754,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="125" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="125" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D125" s="102" t="s">
         <v>89</v>
       </c>
@@ -8791,7 +8792,7 @@
         <v>0.16433159370038652</v>
       </c>
     </row>
-    <row r="126" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="126" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D126" s="102" t="s">
         <v>90</v>
       </c>
@@ -8833,7 +8834,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="127" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="127" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D127" s="102"/>
       <c r="E127" s="102"/>
       <c r="F127" s="102"/>
@@ -8849,7 +8850,7 @@
       <c r="P127" s="109"/>
       <c r="Q127" s="109"/>
     </row>
-    <row r="128" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="128" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D128" s="102"/>
       <c r="E128" s="102"/>
       <c r="F128" s="102"/>
@@ -8865,7 +8866,7 @@
       <c r="P128" s="109"/>
       <c r="Q128" s="109"/>
     </row>
-    <row r="129" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:26" x14ac:dyDescent="0.35">
       <c r="D129" s="110"/>
       <c r="E129" s="141"/>
       <c r="F129" s="142"/>
@@ -8878,7 +8879,7 @@
       <c r="M129" s="144"/>
       <c r="N129" s="144"/>
     </row>
-    <row r="130" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:26" x14ac:dyDescent="0.35">
       <c r="D130" s="110"/>
       <c r="E130" s="141"/>
       <c r="F130" s="142"/>
@@ -8891,7 +8892,7 @@
       <c r="M130" s="144"/>
       <c r="N130" s="144"/>
     </row>
-    <row r="131" spans="2:26" s="311" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="2:26" s="311" customFormat="1" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B131" s="310" t="s">
         <v>66</v>
       </c>
@@ -8902,13 +8903,13 @@
       <c r="F131" s="312"/>
       <c r="G131" s="313"/>
     </row>
-    <row r="132" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:26" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D132" s="309"/>
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
       <c r="G132" s="4"/>
     </row>
-    <row r="133" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:26" x14ac:dyDescent="0.35">
       <c r="D133" s="145" t="s">
         <v>93</v>
       </c>
@@ -8923,8 +8924,8 @@
       <c r="L133" s="147"/>
       <c r="M133" s="147"/>
     </row>
-    <row r="134" spans="2:26" ht="3.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="135" spans="2:26" ht="15.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="2:26" ht="4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="135" spans="2:26" ht="15" x14ac:dyDescent="0.4">
       <c r="D135" s="1" t="s">
         <v>95</v>
       </c>
@@ -8956,7 +8957,7 @@
       <c r="Y135" s="436"/>
       <c r="Z135" s="419"/>
     </row>
-    <row r="136" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:26" x14ac:dyDescent="0.35">
       <c r="D136" s="1" t="s">
         <v>100</v>
       </c>
@@ -8988,7 +8989,7 @@
       <c r="Y136" s="437"/>
       <c r="Z136" s="421"/>
     </row>
-    <row r="137" spans="2:26" ht="15.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="2:26" ht="15" x14ac:dyDescent="0.4">
       <c r="D137" s="1" t="s">
         <v>101</v>
       </c>
@@ -9021,7 +9022,7 @@
       <c r="Y137" s="437"/>
       <c r="Z137" s="421"/>
     </row>
-    <row r="138" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:26" x14ac:dyDescent="0.35">
       <c r="D138" s="157" t="s">
         <v>102</v>
       </c>
@@ -9054,7 +9055,7 @@
       <c r="Y138" s="437"/>
       <c r="Z138" s="421"/>
     </row>
-    <row r="139" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:26" x14ac:dyDescent="0.35">
       <c r="H139" s="149"/>
       <c r="J139" s="152">
         <v>4.4999999999999998E-2</v>
@@ -9078,7 +9079,7 @@
       <c r="Y139" s="437"/>
       <c r="Z139" s="421"/>
     </row>
-    <row r="140" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:26" x14ac:dyDescent="0.35">
       <c r="D140" s="1" t="s">
         <v>103</v>
       </c>
@@ -9111,7 +9112,7 @@
       <c r="Y140" s="437"/>
       <c r="Z140" s="421"/>
     </row>
-    <row r="141" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:26" x14ac:dyDescent="0.35">
       <c r="D141" s="1" t="s">
         <v>104</v>
       </c>
@@ -9143,7 +9144,7 @@
       <c r="Y141" s="437"/>
       <c r="Z141" s="421"/>
     </row>
-    <row r="142" spans="2:26" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="142" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D142" s="157" t="s">
         <v>105</v>
       </c>
@@ -9165,7 +9166,7 @@
       <c r="Y142" s="438"/>
       <c r="Z142" s="423"/>
     </row>
-    <row r="143" spans="2:26" ht="6.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:26" ht="6.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H143" s="149"/>
       <c r="Q143" s="156"/>
       <c r="R143" s="156"/>
@@ -9173,7 +9174,7 @@
       <c r="T143" s="156"/>
       <c r="U143" s="156"/>
     </row>
-    <row r="144" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:26" x14ac:dyDescent="0.35">
       <c r="D144" s="166" t="s">
         <v>106</v>
       </c>
@@ -9186,7 +9187,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="145" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:26" x14ac:dyDescent="0.35">
       <c r="D145" s="29" t="s">
         <v>107</v>
       </c>
@@ -9205,7 +9206,7 @@
       <c r="T145" s="156"/>
       <c r="U145" s="156"/>
     </row>
-    <row r="146" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:26" x14ac:dyDescent="0.35">
       <c r="D146" s="29" t="s">
         <v>108</v>
       </c>
@@ -9224,7 +9225,7 @@
       <c r="T146" s="156"/>
       <c r="U146" s="156"/>
     </row>
-    <row r="147" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:26" x14ac:dyDescent="0.35">
       <c r="D147" s="168" t="s">
         <v>109</v>
       </c>
@@ -9244,7 +9245,7 @@
       <c r="T147" s="156"/>
       <c r="U147" s="156"/>
     </row>
-    <row r="148" spans="2:26" ht="3.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:26" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D148" s="158"/>
       <c r="E148" s="158"/>
       <c r="F148" s="158"/>
@@ -9256,7 +9257,7 @@
       <c r="T148" s="156"/>
       <c r="U148" s="156"/>
     </row>
-    <row r="149" spans="2:26" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="149" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D149" s="258" t="s">
         <v>93</v>
       </c>
@@ -9273,7 +9274,7 @@
       <c r="T149" s="156"/>
       <c r="U149" s="156"/>
     </row>
-    <row r="150" spans="2:26" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="150" spans="2:26" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="D150" s="170" t="s">
         <v>110</v>
       </c>
@@ -9283,22 +9284,22 @@
       <c r="T150" s="156"/>
       <c r="U150" s="156"/>
     </row>
-    <row r="151" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:26" x14ac:dyDescent="0.35">
       <c r="D151" s="170" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="152" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="152" spans="2:26" x14ac:dyDescent="0.35">
       <c r="D152" s="170" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="153" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="153" spans="2:26" x14ac:dyDescent="0.35">
       <c r="D153" s="170" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="156" spans="2:26" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="156" spans="2:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B156" s="315" t="s">
         <v>217</v>
       </c>
@@ -9317,7 +9318,7 @@
       <c r="L156" s="172"/>
       <c r="M156" s="172"/>
     </row>
-    <row r="157" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="157" spans="2:26" x14ac:dyDescent="0.35">
       <c r="D157" s="17" t="s">
         <v>115</v>
       </c>
@@ -9356,7 +9357,7 @@
       <c r="Y157" s="436"/>
       <c r="Z157" s="419"/>
     </row>
-    <row r="158" spans="2:26" ht="6.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="158" spans="2:26" ht="6.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D158" s="170"/>
       <c r="U158" s="420"/>
       <c r="V158" s="437"/>
@@ -9365,7 +9366,7 @@
       <c r="Y158" s="437"/>
       <c r="Z158" s="421"/>
     </row>
-    <row r="159" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="159" spans="2:26" x14ac:dyDescent="0.35">
       <c r="D159" s="174" t="s">
         <v>21</v>
       </c>
@@ -9399,7 +9400,7 @@
       <c r="Y159" s="437"/>
       <c r="Z159" s="421"/>
     </row>
-    <row r="160" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="160" spans="2:26" x14ac:dyDescent="0.35">
       <c r="D160" s="175" t="str">
         <f>"Taxes @ "&amp;TEXT(M39,"0.0%")</f>
         <v>Taxes @ 21.0%</v>
@@ -9435,7 +9436,7 @@
       <c r="Y160" s="437"/>
       <c r="Z160" s="421"/>
     </row>
-    <row r="161" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="161" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D161" s="176" t="s">
         <v>116</v>
       </c>
@@ -9469,7 +9470,7 @@
       <c r="Y161" s="437"/>
       <c r="Z161" s="421"/>
     </row>
-    <row r="162" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="162" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D162" s="178" t="s">
         <v>117</v>
       </c>
@@ -9504,7 +9505,7 @@
       <c r="Y162" s="437"/>
       <c r="Z162" s="421"/>
     </row>
-    <row r="163" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="163" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D163" s="178" t="s">
         <v>118</v>
       </c>
@@ -9539,7 +9540,7 @@
       <c r="Y163" s="437"/>
       <c r="Z163" s="421"/>
     </row>
-    <row r="164" spans="4:26" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="164" spans="4:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D164" s="178" t="s">
         <v>119</v>
       </c>
@@ -9574,7 +9575,7 @@
       <c r="Y164" s="438"/>
       <c r="Z164" s="423"/>
     </row>
-    <row r="165" spans="4:26" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="165" spans="4:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D165" s="180" t="s">
         <v>120</v>
       </c>
@@ -9608,11 +9609,11 @@
         <v>229</v>
       </c>
     </row>
-    <row r="166" spans="4:26" ht="6.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="166" spans="4:26" ht="6.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="D166" s="179"/>
       <c r="G166" s="179"/>
     </row>
-    <row r="167" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="167" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D167" s="179" t="s">
         <v>121</v>
       </c>
@@ -9641,7 +9642,7 @@
         <v>8.9429432425918901E-2</v>
       </c>
     </row>
-    <row r="168" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="168" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D168" s="179" t="s">
         <v>122</v>
       </c>
@@ -9669,7 +9670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="169" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D169" s="179" t="s">
         <v>124</v>
       </c>
@@ -9698,12 +9699,12 @@
         <v>0.65163511485875814</v>
       </c>
     </row>
-    <row r="170" spans="4:26" ht="6.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="170" spans="4:26" ht="6.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D170" s="179"/>
       <c r="E170" s="179"/>
       <c r="F170" s="179"/>
     </row>
-    <row r="171" spans="4:26" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="171" spans="4:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D171" s="183" t="s">
         <v>125</v>
       </c>
@@ -9734,12 +9735,12 @@
         <v>2778.989218156385</v>
       </c>
     </row>
-    <row r="172" spans="4:26" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="172" spans="4:26" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="D172" s="179"/>
       <c r="E172" s="179"/>
       <c r="F172" s="179"/>
     </row>
-    <row r="173" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="173" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D173" s="185" t="s">
         <v>126</v>
       </c>
@@ -9749,7 +9750,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="174" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="174" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D174" s="179"/>
       <c r="E174" s="179"/>
       <c r="F174" s="179"/>
@@ -9764,7 +9765,7 @@
         <v>4264.640064338354</v>
       </c>
     </row>
-    <row r="175" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="175" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D175" s="174" t="str">
         <f>"NPV of UFCF "&amp;TEXT(I157,"0")&amp;" - "&amp;TEXT(M157,"0")</f>
         <v>NPV of UFCF 2023 - 2027</v>
@@ -9783,7 +9784,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="176" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="176" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D176" s="174" t="s">
         <v>129</v>
       </c>
@@ -9802,7 +9803,7 @@
         <v>58157.230603790791</v>
       </c>
     </row>
-    <row r="177" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="177" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D177" s="192" t="s">
         <v>131</v>
       </c>
@@ -9821,7 +9822,7 @@
         <v>9.4249454550193636</v>
       </c>
     </row>
-    <row r="178" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="178" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D178" s="1" t="s">
         <v>133</v>
       </c>
@@ -9830,7 +9831,7 @@
         <v>-3611</v>
       </c>
     </row>
-    <row r="179" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="179" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D179" s="1" t="s">
         <v>134</v>
       </c>
@@ -9852,7 +9853,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="180" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="180" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D180" s="1" t="s">
         <v>137</v>
       </c>
@@ -9877,7 +9878,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="181" spans="2:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="181" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D181" s="203" t="s">
         <v>140</v>
       </c>
@@ -9913,7 +9914,7 @@
       <c r="O181" s="195"/>
       <c r="Q181" s="196"/>
     </row>
-    <row r="182" spans="2:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="182" spans="2:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D182" s="1" t="s">
         <v>141</v>
       </c>
@@ -9951,7 +9952,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="183" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="183" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D183" s="203" t="s">
         <v>135</v>
       </c>
@@ -9984,7 +9985,7 @@
       <c r="P183" s="195"/>
       <c r="Q183" s="195"/>
     </row>
-    <row r="184" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="184" spans="2:17" x14ac:dyDescent="0.35">
       <c r="H184" s="424"/>
       <c r="I184" s="374">
         <f>G149</f>
@@ -10009,7 +10010,7 @@
       <c r="P184" s="212"/>
       <c r="Q184" s="195"/>
     </row>
-    <row r="185" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="185" spans="2:17" x14ac:dyDescent="0.35">
       <c r="H185" s="424"/>
       <c r="I185" s="205">
         <f>I184+$Q$182</f>
@@ -10034,7 +10035,7 @@
       <c r="P185" s="195"/>
       <c r="Q185" s="195"/>
     </row>
-    <row r="186" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="186" spans="2:17" x14ac:dyDescent="0.35">
       <c r="H186" s="424"/>
       <c r="I186" s="205">
         <f>I185+$Q$182</f>
@@ -10059,7 +10060,7 @@
       <c r="P186" s="195"/>
       <c r="Q186" s="195"/>
     </row>
-    <row r="187" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="187" spans="2:17" x14ac:dyDescent="0.35">
       <c r="I187" s="195"/>
       <c r="J187" s="195"/>
       <c r="K187" s="195"/>
@@ -10067,7 +10068,7 @@
       <c r="M187" s="195"/>
       <c r="N187" s="195"/>
     </row>
-    <row r="188" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="188" spans="2:17" x14ac:dyDescent="0.35">
       <c r="I188" s="195"/>
       <c r="J188" s="195"/>
       <c r="K188" s="195"/>
@@ -10075,7 +10076,7 @@
       <c r="M188" s="195"/>
       <c r="N188" s="195"/>
     </row>
-    <row r="189" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="189" spans="2:17" x14ac:dyDescent="0.35">
       <c r="I189" s="195"/>
       <c r="J189" s="195"/>
       <c r="K189" s="195"/>
@@ -10083,7 +10084,7 @@
       <c r="M189" s="195"/>
       <c r="N189" s="195"/>
     </row>
-    <row r="190" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="190" spans="2:17" x14ac:dyDescent="0.35">
       <c r="I190" s="195"/>
       <c r="J190" s="195"/>
       <c r="K190" s="195"/>
@@ -10091,7 +10092,7 @@
       <c r="M190" s="195"/>
       <c r="N190" s="195"/>
     </row>
-    <row r="191" spans="2:17" s="311" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="2:17" s="311" customFormat="1" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B191" s="310" t="s">
         <v>91</v>
       </c>
@@ -10102,13 +10103,13 @@
       <c r="F191" s="312"/>
       <c r="G191" s="313"/>
     </row>
-    <row r="192" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="192" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D192" s="309"/>
       <c r="E192" s="3"/>
       <c r="F192" s="3"/>
       <c r="G192" s="4"/>
     </row>
-    <row r="193" spans="4:26" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="193" spans="4:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D193" s="213" t="s">
         <v>144</v>
       </c>
@@ -10123,7 +10124,7 @@
       <c r="L193" s="214"/>
       <c r="M193" s="214"/>
     </row>
-    <row r="194" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="194" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D194" s="17" t="s">
         <v>146</v>
       </c>
@@ -10157,7 +10158,7 @@
       <c r="Y194" s="436"/>
       <c r="Z194" s="419"/>
     </row>
-    <row r="195" spans="4:26" ht="6.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="195" spans="4:26" ht="6.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D195" s="156"/>
       <c r="E195" s="219"/>
       <c r="F195" s="219"/>
@@ -10173,7 +10174,7 @@
       <c r="Y195" s="437"/>
       <c r="Z195" s="421"/>
     </row>
-    <row r="196" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="196" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D196" s="156" t="s">
         <v>147</v>
       </c>
@@ -10208,7 +10209,7 @@
       <c r="Y196" s="437"/>
       <c r="Z196" s="421"/>
     </row>
-    <row r="197" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="197" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D197" s="156" t="s">
         <v>149</v>
       </c>
@@ -10244,7 +10245,7 @@
       <c r="Y197" s="437"/>
       <c r="Z197" s="421"/>
     </row>
-    <row r="198" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="198" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D198" s="156" t="s">
         <v>151</v>
       </c>
@@ -10283,7 +10284,7 @@
       <c r="Y198" s="437"/>
       <c r="Z198" s="421"/>
     </row>
-    <row r="199" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="199" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D199" s="156" t="s">
         <v>153</v>
       </c>
@@ -10322,7 +10323,7 @@
       <c r="Y199" s="437"/>
       <c r="Z199" s="421"/>
     </row>
-    <row r="200" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="200" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D200" s="156" t="s">
         <v>155</v>
       </c>
@@ -10345,7 +10346,7 @@
       <c r="Y200" s="437"/>
       <c r="Z200" s="421"/>
     </row>
-    <row r="201" spans="4:26" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="201" spans="4:26" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D201" s="156" t="s">
         <v>156</v>
       </c>
@@ -10368,7 +10369,7 @@
       <c r="Y201" s="438"/>
       <c r="Z201" s="423"/>
     </row>
-    <row r="202" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="202" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D202" s="222" t="s">
         <v>144</v>
       </c>
@@ -10386,10 +10387,10 @@
         <v>230</v>
       </c>
     </row>
-    <row r="203" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="203" spans="4:26" x14ac:dyDescent="0.35">
       <c r="H203" s="219"/>
     </row>
-    <row r="204" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="204" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D204" s="156"/>
       <c r="E204" s="156"/>
       <c r="F204" s="156"/>
@@ -10399,7 +10400,7 @@
       <c r="J204" s="219"/>
       <c r="K204" s="219"/>
     </row>
-    <row r="205" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="205" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D205" s="223"/>
       <c r="E205" s="223"/>
       <c r="F205" s="223"/>
@@ -10422,7 +10423,7 @@
       <c r="O205" s="227"/>
       <c r="P205" s="228"/>
     </row>
-    <row r="206" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="206" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D206" s="229" t="s">
         <v>161</v>
       </c>
@@ -10459,7 +10460,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="207" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="207" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D207" s="236" t="s">
         <v>164</v>
       </c>
@@ -10493,7 +10494,7 @@
       </c>
       <c r="T207" s="349"/>
     </row>
-    <row r="208" spans="4:26" x14ac:dyDescent="0.45">
+    <row r="208" spans="4:26" x14ac:dyDescent="0.35">
       <c r="D208" s="236" t="s">
         <v>165</v>
       </c>
@@ -10527,7 +10528,7 @@
       </c>
       <c r="T208" s="349"/>
     </row>
-    <row r="209" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="209" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D209" s="236" t="s">
         <v>166</v>
       </c>
@@ -10561,7 +10562,7 @@
       </c>
       <c r="T209" s="349"/>
     </row>
-    <row r="210" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="210" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D210" s="236" t="s">
         <v>167</v>
       </c>
@@ -10595,7 +10596,7 @@
       </c>
       <c r="T210" s="349"/>
     </row>
-    <row r="211" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="211" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D211" s="236" t="s">
         <v>169</v>
       </c>
@@ -10629,7 +10630,7 @@
       </c>
       <c r="T211" s="349"/>
     </row>
-    <row r="212" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="212" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D212" s="236" t="s">
         <v>170</v>
       </c>
@@ -10663,7 +10664,7 @@
       </c>
       <c r="T212" s="349"/>
     </row>
-    <row r="213" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="213" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D213" s="236" t="s">
         <v>171</v>
       </c>
@@ -10697,7 +10698,7 @@
       </c>
       <c r="T213" s="349"/>
     </row>
-    <row r="214" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="214" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D214" s="156"/>
       <c r="E214" s="156"/>
       <c r="F214" s="156"/>
@@ -10713,7 +10714,7 @@
       <c r="P214" s="244"/>
       <c r="T214" s="350"/>
     </row>
-    <row r="215" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="215" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D215" s="245" t="s">
         <v>172</v>
       </c>
@@ -10747,7 +10748,7 @@
         <v>12.926959327726898</v>
       </c>
     </row>
-    <row r="216" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="216" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D216" s="245" t="s">
         <v>174</v>
       </c>
@@ -10781,7 +10782,7 @@
         <v>8.8117420593299283</v>
       </c>
     </row>
-    <row r="217" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="217" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D217" s="245" t="s">
         <v>216</v>
       </c>
@@ -10815,7 +10816,7 @@
         <v>10.031605664758887</v>
       </c>
     </row>
-    <row r="218" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="218" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D218" s="156"/>
       <c r="E218" s="156"/>
       <c r="F218" s="156"/>
@@ -10847,13 +10848,13 @@
         <v>1.7211783283985982</v>
       </c>
     </row>
-    <row r="219" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="219" spans="4:21" x14ac:dyDescent="0.35">
       <c r="H219" s="219"/>
       <c r="I219" s="219"/>
       <c r="J219" s="219"/>
       <c r="K219" s="219"/>
     </row>
-    <row r="220" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="220" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D220" s="247" t="str">
         <f>D4&amp;" Implied Enterprise Value"</f>
         <v>Activsion Blizzard Inc. Implied Enterprise Value</v>
@@ -10895,13 +10896,13 @@
         <v>28658.12146036432</v>
       </c>
     </row>
-    <row r="221" spans="4:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="221" spans="4:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="H221" s="219"/>
       <c r="I221" s="219"/>
       <c r="J221" s="219"/>
       <c r="K221" s="219"/>
     </row>
-    <row r="222" spans="4:21" ht="28.9" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="222" spans="4:21" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D222" s="270" t="s">
         <v>202</v>
       </c>
@@ -10926,7 +10927,7 @@
       </c>
       <c r="P222" s="426"/>
     </row>
-    <row r="223" spans="4:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="223" spans="4:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D223" s="273" t="s">
         <v>198</v>
       </c>
@@ -10943,7 +10944,7 @@
       </c>
       <c r="U223" s="419"/>
     </row>
-    <row r="224" spans="4:21" x14ac:dyDescent="0.45">
+    <row r="224" spans="4:21" x14ac:dyDescent="0.35">
       <c r="D224" s="273" t="s">
         <v>197</v>
       </c>
@@ -10972,7 +10973,7 @@
       <c r="T224" s="420"/>
       <c r="U224" s="421"/>
     </row>
-    <row r="225" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="225" spans="2:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D225" s="273" t="s">
         <v>199</v>
       </c>
@@ -10996,7 +10997,7 @@
       <c r="T225" s="420"/>
       <c r="U225" s="421"/>
     </row>
-    <row r="226" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="226" spans="2:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D226" s="273" t="s">
         <v>200</v>
       </c>
@@ -11020,7 +11021,7 @@
       <c r="T226" s="420"/>
       <c r="U226" s="421"/>
     </row>
-    <row r="227" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="227" spans="2:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D227" s="281" t="s">
         <v>201</v>
       </c>
@@ -11047,7 +11048,7 @@
       <c r="T227" s="420"/>
       <c r="U227" s="421"/>
     </row>
-    <row r="228" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="228" spans="2:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H228" s="219"/>
       <c r="I228" s="219"/>
       <c r="J228" s="219"/>
@@ -11059,7 +11060,7 @@
       <c r="T228" s="420"/>
       <c r="U228" s="421"/>
     </row>
-    <row r="229" spans="2:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="229" spans="2:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H229" s="219"/>
       <c r="I229" s="219"/>
       <c r="J229" s="219"/>
@@ -11071,7 +11072,7 @@
       <c r="T229" s="420"/>
       <c r="U229" s="421"/>
     </row>
-    <row r="230" spans="2:21" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="230" spans="2:21" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D230" s="156"/>
       <c r="E230" s="156"/>
       <c r="F230" s="156"/>
@@ -11087,16 +11088,16 @@
       <c r="T230" s="422"/>
       <c r="U230" s="423"/>
     </row>
-    <row r="231" spans="2:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="231" spans="2:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="N231" s="433"/>
       <c r="O231" s="434"/>
       <c r="P231" s="434"/>
       <c r="Q231" s="435"/>
     </row>
-    <row r="232" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="232" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D232" s="187"/>
     </row>
-    <row r="233" spans="2:21" s="311" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="233" spans="2:21" s="311" customFormat="1" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B233" s="310" t="s">
         <v>178</v>
       </c>
@@ -11107,14 +11108,14 @@
       <c r="F233" s="312"/>
       <c r="G233" s="313"/>
     </row>
-    <row r="234" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="234" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D234" s="309"/>
       <c r="E234" s="3"/>
       <c r="F234" s="3"/>
       <c r="G234" s="4"/>
     </row>
-    <row r="235" spans="2:21" ht="3.95" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="236" spans="2:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="235" spans="2:21" ht="4" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="236" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D236" s="10" t="s">
         <v>179</v>
       </c>
@@ -11136,7 +11137,7 @@
       <c r="P236" s="15"/>
       <c r="Q236" s="15"/>
     </row>
-    <row r="237" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="237" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D237" s="187"/>
       <c r="G237" s="18"/>
       <c r="H237" s="19" t="s">
@@ -11183,13 +11184,13 @@
       </c>
       <c r="U237" s="419"/>
     </row>
-    <row r="238" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="238" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D238" s="187"/>
       <c r="H238" s="26"/>
       <c r="T238" s="420"/>
       <c r="U238" s="421"/>
     </row>
-    <row r="239" spans="2:21" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="239" spans="2:21" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D239" s="187" t="s">
         <v>180</v>
       </c>
@@ -11198,7 +11199,7 @@
       <c r="T239" s="420"/>
       <c r="U239" s="421"/>
     </row>
-    <row r="240" spans="2:21" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="240" spans="2:21" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D240" s="29" t="s">
         <v>181</v>
       </c>
@@ -11244,7 +11245,7 @@
       <c r="T240" s="420"/>
       <c r="U240" s="421"/>
     </row>
-    <row r="241" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="241" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D241" s="29" t="s">
         <v>182</v>
       </c>
@@ -11290,7 +11291,7 @@
       <c r="T241" s="420"/>
       <c r="U241" s="421"/>
     </row>
-    <row r="242" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="242" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D242" s="29" t="s">
         <v>183</v>
       </c>
@@ -11336,7 +11337,7 @@
       <c r="T242" s="420"/>
       <c r="U242" s="421"/>
     </row>
-    <row r="243" spans="4:23" ht="5.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="243" spans="4:23" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D243" s="29"/>
       <c r="H243" s="251"/>
       <c r="I243" s="252"/>
@@ -11351,7 +11352,7 @@
       <c r="T243" s="420"/>
       <c r="U243" s="421"/>
     </row>
-    <row r="244" spans="4:23" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="244" spans="4:23" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D244" s="34" t="s">
         <v>184</v>
       </c>
@@ -11361,7 +11362,7 @@
       <c r="T244" s="422"/>
       <c r="U244" s="423"/>
     </row>
-    <row r="245" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="245" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D245" s="29" t="s">
         <v>185</v>
       </c>
@@ -11405,7 +11406,7 @@
         <v>7.2271131785234806</v>
       </c>
     </row>
-    <row r="246" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="246" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D246" s="29" t="s">
         <v>186</v>
       </c>
@@ -11449,7 +11450,7 @@
         <v>5.1700343128995758</v>
       </c>
     </row>
-    <row r="247" spans="4:23" ht="5.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="247" spans="4:23" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D247" s="29"/>
       <c r="H247" s="251"/>
       <c r="I247" s="194"/>
@@ -11462,14 +11463,14 @@
       <c r="P247" s="194"/>
       <c r="Q247" s="390"/>
     </row>
-    <row r="248" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="248" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D248" s="34" t="s">
         <v>187</v>
       </c>
       <c r="L248" s="250"/>
       <c r="Q248" s="389"/>
     </row>
-    <row r="249" spans="4:23" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="249" spans="4:23" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D249" s="29" t="s">
         <v>188</v>
       </c>
@@ -11510,7 +11511,7 @@
         <v>48.777272727272738</v>
       </c>
     </row>
-    <row r="250" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="250" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D250" s="29" t="s">
         <v>189</v>
       </c>
@@ -11555,14 +11556,14 @@
       </c>
       <c r="W250" s="419"/>
     </row>
-    <row r="251" spans="4:23" ht="5.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="251" spans="4:23" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D251" s="29"/>
       <c r="L251" s="250"/>
       <c r="Q251" s="389"/>
       <c r="V251" s="420"/>
       <c r="W251" s="421"/>
     </row>
-    <row r="252" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="252" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D252" s="34" t="s">
         <v>190</v>
       </c>
@@ -11571,7 +11572,7 @@
       <c r="V252" s="420"/>
       <c r="W252" s="421"/>
     </row>
-    <row r="253" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="253" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D253" s="29" t="s">
         <v>191</v>
       </c>
@@ -11617,7 +11618,7 @@
       <c r="V253" s="420"/>
       <c r="W253" s="421"/>
     </row>
-    <row r="254" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="254" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D254" s="29" t="s">
         <v>192</v>
       </c>
@@ -11663,7 +11664,7 @@
       <c r="V254" s="420"/>
       <c r="W254" s="421"/>
     </row>
-    <row r="255" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="255" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D255" s="29" t="s">
         <v>193</v>
       </c>
@@ -11709,13 +11710,13 @@
       <c r="V255" s="420"/>
       <c r="W255" s="421"/>
     </row>
-    <row r="256" spans="4:23" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="256" spans="4:23" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
       <c r="L256" s="250"/>
       <c r="Q256" s="389"/>
       <c r="V256" s="420"/>
       <c r="W256" s="421"/>
     </row>
-    <row r="257" spans="4:23" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="257" spans="4:23" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D257" s="34" t="s">
         <v>194</v>
       </c>
@@ -11724,7 +11725,7 @@
       <c r="V257" s="422"/>
       <c r="W257" s="423"/>
     </row>
-    <row r="258" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="258" spans="4:23" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D258" s="29" t="s">
         <v>195</v>
       </c>
@@ -11768,7 +11769,7 @@
         <v>93.799857750120054</v>
       </c>
     </row>
-    <row r="259" spans="4:23" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="259" spans="4:23" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D259" s="29" t="s">
         <v>196</v>
       </c>
@@ -11812,7 +11813,7 @@
         <v>90.229060437308974</v>
       </c>
     </row>
-    <row r="1000" spans="648:648" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="1000" spans="648:648" ht="15.5" x14ac:dyDescent="0.35">
       <c r="XX1000" s="406">
         <v>102911</v>
       </c>
@@ -11932,23 +11933,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F8450BE-7803-4A8C-B61C-9F1D6BE703C0}">
   <dimension ref="B4:Z259"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" style="34" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="3.73046875" style="1" hidden="1" customWidth="1"/>
-    <col min="4" max="7" width="13.73046875" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="5.73046875" style="1" hidden="1" customWidth="1"/>
-    <col min="9" max="17" width="13.59765625" style="1" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="1.73046875" style="1" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="7.73046875" style="1" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="16.86328125" style="1" hidden="1" customWidth="1"/>
-    <col min="21" max="26" width="9.1328125" style="1" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="9.08984375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" style="34" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="3.7265625" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="7" width="13.7265625" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="5.7265625" style="1" hidden="1" customWidth="1"/>
+    <col min="9" max="17" width="13.6328125" style="1" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="1.7265625" style="1" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="7.7265625" style="1" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="16.81640625" style="1" hidden="1" customWidth="1"/>
+    <col min="21" max="26" width="9.08984375" style="1" hidden="1" customWidth="1"/>
     <col min="27" max="30" width="0" style="1" hidden="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.1328125" style="1"/>
+    <col min="31" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:23" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="D4" s="2" t="s">
         <v>0</v>
       </c>
@@ -11957,7 +11958,7 @@
       <c r="G4" s="4"/>
       <c r="U4"/>
     </row>
-    <row r="5" spans="2:23" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:23" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="D5" s="5" t="s">
         <v>1</v>
       </c>
@@ -11977,7 +11978,7 @@
       <c r="R5" s="8"/>
       <c r="S5" s="8"/>
     </row>
-    <row r="7" spans="2:23" s="311" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:23" s="311" customFormat="1" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="310" t="s">
         <v>2</v>
       </c>
@@ -11988,7 +11989,7 @@
       <c r="F7" s="312"/>
       <c r="G7" s="313"/>
     </row>
-    <row r="9" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:23" x14ac:dyDescent="0.35">
       <c r="B9" s="307"/>
       <c r="C9" s="9"/>
       <c r="D9" s="10" t="s">
@@ -12015,7 +12016,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D10" s="17" t="s">
         <v>7</v>
       </c>
@@ -12065,10 +12066,10 @@
         <v>2022 - 2027</v>
       </c>
     </row>
-    <row r="11" spans="2:23" ht="3.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:23" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H11" s="26"/>
     </row>
-    <row r="12" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D12" s="1" t="s">
         <v>9</v>
       </c>
@@ -12115,7 +12116,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D13" s="29" t="s">
         <v>11</v>
       </c>
@@ -12161,7 +12162,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="14" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D14" s="31" t="s">
         <v>12</v>
       </c>
@@ -12210,7 +12211,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="15" spans="2:23" ht="6.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:23" ht="6.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D15" s="34"/>
       <c r="E15" s="34"/>
       <c r="F15" s="34"/>
@@ -12228,7 +12229,7 @@
       <c r="S15" s="34"/>
       <c r="T15" s="34"/>
     </row>
-    <row r="16" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:23" x14ac:dyDescent="0.35">
       <c r="D16" s="29" t="s">
         <v>13</v>
       </c>
@@ -12273,7 +12274,7 @@
       <c r="S16" s="34"/>
       <c r="T16" s="34"/>
     </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D17" s="29" t="s">
         <v>14</v>
       </c>
@@ -12318,7 +12319,7 @@
       <c r="S17" s="34"/>
       <c r="T17" s="34"/>
     </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D18" s="39" t="s">
         <v>15</v>
       </c>
@@ -12363,7 +12364,7 @@
       <c r="S18" s="34"/>
       <c r="T18" s="34"/>
     </row>
-    <row r="19" spans="2:21" ht="6.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:21" ht="6.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D19" s="34"/>
       <c r="E19" s="34"/>
       <c r="F19" s="34"/>
@@ -12381,7 +12382,7 @@
       <c r="S19" s="34"/>
       <c r="T19" s="34"/>
     </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D20" s="29" t="s">
         <v>16</v>
       </c>
@@ -12421,7 +12422,7 @@
       <c r="S20" s="34"/>
       <c r="T20" s="34"/>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D21" s="29" t="s">
         <v>17</v>
       </c>
@@ -12466,7 +12467,7 @@
       <c r="S21" s="34"/>
       <c r="T21" s="34"/>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D22" s="40" t="s">
         <v>18</v>
       </c>
@@ -12510,7 +12511,7 @@
       <c r="S22" s="34"/>
       <c r="T22" s="34"/>
     </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D23" s="29" t="s">
         <v>19</v>
       </c>
@@ -12555,7 +12556,7 @@
       <c r="S23" s="34"/>
       <c r="T23" s="34"/>
     </row>
-    <row r="24" spans="2:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="24" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D24" s="41" t="s">
         <v>20</v>
       </c>
@@ -12600,12 +12601,12 @@
       <c r="S24" s="34"/>
       <c r="T24" s="34"/>
     </row>
-    <row r="25" spans="2:21" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:21" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="L25" s="44"/>
       <c r="S25" s="34"/>
       <c r="T25" s="34"/>
     </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D26" s="1" t="s">
         <v>21</v>
       </c>
@@ -12647,7 +12648,7 @@
       <c r="S26" s="34"/>
       <c r="T26" s="34"/>
     </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D27" s="29" t="s">
         <v>22</v>
       </c>
@@ -12689,7 +12690,7 @@
       <c r="S27" s="34"/>
       <c r="T27" s="34"/>
     </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D28" s="47" t="s">
         <v>23</v>
       </c>
@@ -12735,7 +12736,7 @@
       <c r="S28" s="34"/>
       <c r="T28" s="34"/>
     </row>
-    <row r="29" spans="2:21" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:21" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B29" s="308" t="s">
         <v>24</v>
       </c>
@@ -12748,7 +12749,7 @@
       <c r="T29" s="1"/>
       <c r="U29" s="1"/>
     </row>
-    <row r="30" spans="2:21" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:21" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B30" s="34"/>
       <c r="C30" s="1"/>
       <c r="D30" s="51" t="s">
@@ -12764,7 +12765,7 @@
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
     </row>
-    <row r="31" spans="2:21" ht="3.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:21" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H31" s="26"/>
       <c r="L31" s="52">
         <v>0</v>
@@ -12773,7 +12774,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D32" s="53" t="s">
         <v>27</v>
       </c>
@@ -12817,7 +12818,7 @@
         <v>-1.2499999999999997E-2</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D33" s="53" t="s">
         <v>29</v>
       </c>
@@ -12863,7 +12864,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D34" s="53" t="s">
         <v>30</v>
       </c>
@@ -12909,7 +12910,7 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D35" s="53" t="s">
         <v>31</v>
       </c>
@@ -12955,7 +12956,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="36" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D36" s="53" t="s">
         <v>32</v>
       </c>
@@ -13001,7 +13002,7 @@
         <v>-5.4906935372091899E-4</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D37" s="53" t="s">
         <v>33</v>
       </c>
@@ -13044,7 +13045,7 @@
       <c r="R37" s="59"/>
       <c r="S37" s="65"/>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D38" s="53" t="s">
         <v>34</v>
       </c>
@@ -13089,7 +13090,7 @@
       <c r="R38" s="59"/>
       <c r="S38" s="59"/>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D39" s="53" t="s">
         <v>35</v>
       </c>
@@ -13133,7 +13134,7 @@
       <c r="R39" s="59"/>
       <c r="S39" s="59"/>
     </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D40" s="53"/>
       <c r="E40" s="53"/>
       <c r="F40" s="53"/>
@@ -13151,7 +13152,7 @@
       <c r="R40" s="59"/>
       <c r="S40" s="59"/>
     </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D41" s="53"/>
       <c r="E41" s="53"/>
       <c r="F41" s="53"/>
@@ -13169,7 +13170,7 @@
       <c r="R41" s="59"/>
       <c r="S41" s="59"/>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D42" s="53"/>
       <c r="E42" s="53"/>
       <c r="F42" s="53"/>
@@ -13187,7 +13188,7 @@
       <c r="R42" s="59"/>
       <c r="S42" s="59"/>
     </row>
-    <row r="44" spans="2:19" s="311" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="2:19" s="311" customFormat="1" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B44" s="310" t="s">
         <v>36</v>
       </c>
@@ -13198,7 +13199,7 @@
       <c r="F44" s="312"/>
       <c r="G44" s="313"/>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B46" s="307"/>
       <c r="C46" s="9"/>
       <c r="D46" s="10" t="s">
@@ -13222,7 +13223,7 @@
       <c r="P46" s="15"/>
       <c r="Q46" s="15"/>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.35">
       <c r="D47" s="17" t="s">
         <v>7</v>
       </c>
@@ -13265,7 +13266,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="48" spans="2:19" ht="3.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:19" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B48" s="307"/>
       <c r="C48" s="9"/>
       <c r="D48" s="18"/>
@@ -13283,7 +13284,7 @@
       <c r="P48" s="70"/>
       <c r="Q48" s="70"/>
     </row>
-    <row r="49" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="49" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D49" s="71" t="s">
         <v>38</v>
       </c>
@@ -13326,7 +13327,7 @@
         <v>17391.407041119543</v>
       </c>
     </row>
-    <row r="50" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="50" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D50" s="71" t="s">
         <v>39</v>
       </c>
@@ -13369,7 +13370,7 @@
         <v>4932</v>
       </c>
     </row>
-    <row r="51" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="51" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D51" s="71" t="s">
         <v>40</v>
       </c>
@@ -13412,7 +13413,7 @@
         <v>2434.8081120644533</v>
       </c>
     </row>
-    <row r="52" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="52" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D52" s="71" t="s">
         <v>41</v>
       </c>
@@ -13455,7 +13456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="53" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D53" s="71" t="s">
         <v>42</v>
       </c>
@@ -13498,7 +13499,7 @@
         <v>2956.5527075068362</v>
       </c>
     </row>
-    <row r="54" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="54" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D54" s="73" t="s">
         <v>43</v>
       </c>
@@ -13541,7 +13542,7 @@
         <v>27714.76786069083</v>
       </c>
     </row>
-    <row r="55" spans="4:17" ht="6.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="4:17" ht="6.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D55" s="76"/>
       <c r="E55" s="76"/>
       <c r="F55" s="76"/>
@@ -13557,7 +13558,7 @@
       <c r="P55" s="77"/>
       <c r="Q55" s="77"/>
     </row>
-    <row r="56" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="56" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D56" s="71" t="s">
         <v>44</v>
       </c>
@@ -13600,7 +13601,7 @@
         <v>-466.82948215661816</v>
       </c>
     </row>
-    <row r="57" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="57" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D57" s="71" t="s">
         <v>45</v>
       </c>
@@ -13638,7 +13639,7 @@
         <v>2792</v>
       </c>
     </row>
-    <row r="58" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="58" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D58" s="71" t="s">
         <v>46</v>
       </c>
@@ -13676,7 +13677,7 @@
         <v>9929</v>
       </c>
     </row>
-    <row r="59" spans="4:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="59" spans="4:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D59" s="79" t="s">
         <v>47</v>
       </c>
@@ -13719,7 +13720,7 @@
         <v>39968.938378534207</v>
       </c>
     </row>
-    <row r="60" spans="4:17" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="4:17" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="D60" s="83"/>
       <c r="E60" s="83"/>
       <c r="F60" s="83"/>
@@ -13735,7 +13736,7 @@
       <c r="P60" s="77"/>
       <c r="Q60" s="77"/>
     </row>
-    <row r="61" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="61" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D61" s="84" t="s">
         <v>48</v>
       </c>
@@ -13778,7 +13779,7 @@
         <v>603.83241179198433</v>
       </c>
     </row>
-    <row r="62" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="62" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D62" s="84" t="s">
         <v>49</v>
       </c>
@@ -13821,7 +13822,7 @@
         <v>3231</v>
       </c>
     </row>
-    <row r="63" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="63" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D63" s="85" t="s">
         <v>50</v>
       </c>
@@ -13864,7 +13865,7 @@
         <v>3834.8324117919842</v>
       </c>
     </row>
-    <row r="64" spans="4:17" ht="6.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="4:17" ht="6.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D64" s="87"/>
       <c r="E64" s="87"/>
       <c r="F64" s="87"/>
@@ -13880,7 +13881,7 @@
       <c r="P64" s="77"/>
       <c r="Q64" s="77"/>
     </row>
-    <row r="65" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="65" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D65" s="84" t="s">
         <v>51</v>
       </c>
@@ -13923,7 +13924,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="66" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="66" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D66" s="84" t="s">
         <v>52</v>
       </c>
@@ -13959,7 +13960,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="67" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="67" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D67" s="88" t="s">
         <v>53</v>
       </c>
@@ -14002,7 +14003,7 @@
         <v>6669.8324117919838</v>
       </c>
     </row>
-    <row r="68" spans="4:19" ht="6.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="4:19" ht="6.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D68" s="89"/>
       <c r="E68" s="89"/>
       <c r="F68" s="89"/>
@@ -14018,7 +14019,7 @@
       <c r="P68" s="91"/>
       <c r="Q68" s="91"/>
     </row>
-    <row r="69" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="69" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D69" s="87" t="s">
         <v>54</v>
       </c>
@@ -14061,7 +14062,7 @@
         <v>33299.105966742223</v>
       </c>
     </row>
-    <row r="70" spans="4:19" ht="6.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="4:19" ht="6.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D70" s="87"/>
       <c r="E70" s="87"/>
       <c r="F70" s="87"/>
@@ -14077,7 +14078,7 @@
       <c r="P70" s="90"/>
       <c r="Q70" s="90"/>
     </row>
-    <row r="71" spans="4:19" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="71" spans="4:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D71" s="79" t="s">
         <v>55</v>
       </c>
@@ -14120,7 +14121,7 @@
         <v>39968.938378534207</v>
       </c>
     </row>
-    <row r="72" spans="4:19" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="4:19" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="D72" s="92" t="s">
         <v>56</v>
       </c>
@@ -14162,7 +14163,7 @@
       </c>
       <c r="R72" s="201"/>
     </row>
-    <row r="73" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="73" spans="4:19" x14ac:dyDescent="0.35">
       <c r="H73" s="26"/>
       <c r="I73" s="94"/>
       <c r="J73" s="94"/>
@@ -14174,7 +14175,7 @@
       <c r="P73" s="94"/>
       <c r="Q73" s="94"/>
     </row>
-    <row r="74" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="74" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D74" s="51" t="s">
         <v>57</v>
       </c>
@@ -14194,7 +14195,7 @@
       <c r="P74"/>
       <c r="Q74"/>
     </row>
-    <row r="75" spans="4:19" ht="3.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="4:19" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H75" s="26"/>
       <c r="L75" s="52">
         <v>0</v>
@@ -14203,7 +14204,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="76" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="76" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D76" s="97" t="s">
         <v>58</v>
       </c>
@@ -14245,7 +14246,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="77" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="77" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D77" s="97" t="s">
         <v>59</v>
       </c>
@@ -14288,7 +14289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="78" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D78" s="97" t="s">
         <v>60</v>
       </c>
@@ -14330,7 +14331,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="79" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="79" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D79" s="102" t="s">
         <v>61</v>
       </c>
@@ -14372,7 +14373,7 @@
         <v>234.90263671875005</v>
       </c>
     </row>
-    <row r="80" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="80" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D80" s="102" t="s">
         <v>62</v>
       </c>
@@ -14413,7 +14414,7 @@
         <v>1.3506760133446791E-2</v>
       </c>
     </row>
-    <row r="81" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D81" s="110" t="s">
         <v>63</v>
       </c>
@@ -14455,7 +14456,7 @@
         <v>0.124</v>
       </c>
     </row>
-    <row r="82" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D82" s="97" t="s">
         <v>64</v>
       </c>
@@ -14497,7 +14498,7 @@
         <v>0.39800000000000002</v>
       </c>
     </row>
-    <row r="83" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D83" s="110" t="s">
         <v>65</v>
       </c>
@@ -14527,7 +14528,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="84" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D84" s="110"/>
       <c r="E84" s="110"/>
       <c r="F84" s="110"/>
@@ -14543,7 +14544,7 @@
       <c r="P84" s="105"/>
       <c r="Q84" s="105"/>
     </row>
-    <row r="85" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D85" s="110"/>
       <c r="E85" s="110"/>
       <c r="F85" s="110"/>
@@ -14559,7 +14560,7 @@
       <c r="P85" s="105"/>
       <c r="Q85" s="105"/>
     </row>
-    <row r="86" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D86" s="110"/>
       <c r="E86" s="110"/>
       <c r="F86" s="110"/>
@@ -14575,10 +14576,10 @@
       <c r="P86" s="105"/>
       <c r="Q86" s="105"/>
     </row>
-    <row r="87" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:17" x14ac:dyDescent="0.35">
       <c r="H87" s="26"/>
     </row>
-    <row r="88" spans="2:17" s="311" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="2:17" s="311" customFormat="1" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B88" s="310" t="s">
         <v>66</v>
       </c>
@@ -14589,10 +14590,10 @@
       <c r="F88" s="312"/>
       <c r="G88" s="313"/>
     </row>
-    <row r="89" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:17" x14ac:dyDescent="0.35">
       <c r="H89" s="26"/>
     </row>
-    <row r="90" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B90" s="307"/>
       <c r="C90" s="9"/>
       <c r="D90" s="10" t="s">
@@ -14616,7 +14617,7 @@
       <c r="P90" s="15"/>
       <c r="Q90" s="15"/>
     </row>
-    <row r="91" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D91" s="17" t="s">
         <v>7</v>
       </c>
@@ -14659,10 +14660,10 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="92" spans="2:17" ht="3.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:17" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H92" s="26"/>
     </row>
-    <row r="93" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D93" s="113" t="s">
         <v>68</v>
       </c>
@@ -14705,7 +14706,7 @@
         <v>4578.5087084312108</v>
       </c>
     </row>
-    <row r="94" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D94" s="116" t="s">
         <v>22</v>
       </c>
@@ -14748,7 +14749,7 @@
         <v>379.19914731031537</v>
       </c>
     </row>
-    <row r="95" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D95" s="116" t="s">
         <v>70</v>
       </c>
@@ -14791,7 +14792,7 @@
         <v>597.3158754194842</v>
       </c>
     </row>
-    <row r="96" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D96" s="118" t="s">
         <v>71</v>
       </c>
@@ -14833,7 +14834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="97" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D97" s="119" t="s">
         <v>72</v>
       </c>
@@ -14851,7 +14852,7 @@
       <c r="P97" s="114"/>
       <c r="Q97" s="114"/>
     </row>
-    <row r="98" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="98" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D98" s="120" t="s">
         <v>73</v>
       </c>
@@ -14894,7 +14895,7 @@
         <v>-221.34619200585939</v>
       </c>
     </row>
-    <row r="99" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="99" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D99" s="120" t="s">
         <v>41</v>
       </c>
@@ -14937,7 +14938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="100" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D100" s="120" t="s">
         <v>42</v>
       </c>
@@ -14980,7 +14981,7 @@
         <v>-268.77751886425813</v>
       </c>
     </row>
-    <row r="101" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="101" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D101" s="120" t="s">
         <v>48</v>
       </c>
@@ -15023,7 +15024,7 @@
         <v>35.288907182648472</v>
       </c>
     </row>
-    <row r="102" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="102" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D102" s="120" t="s">
         <v>49</v>
       </c>
@@ -15066,7 +15067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="103" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D103" s="120" t="s">
         <v>74</v>
       </c>
@@ -15102,7 +15103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="104" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D104" s="121" t="s">
         <v>75</v>
       </c>
@@ -15145,7 +15146,7 @@
         <v>5100.1889274735413</v>
       </c>
     </row>
-    <row r="105" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="105" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D105" s="125"/>
       <c r="E105" s="125"/>
       <c r="F105" s="125"/>
@@ -15161,7 +15162,7 @@
       <c r="P105" s="114"/>
       <c r="Q105" s="114"/>
     </row>
-    <row r="106" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="106" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D106" s="118" t="s">
         <v>61</v>
       </c>
@@ -15204,7 +15205,7 @@
         <v>-234.90263671875005</v>
       </c>
     </row>
-    <row r="107" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="107" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D107" s="118" t="s">
         <v>76</v>
       </c>
@@ -15246,7 +15247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="108" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D108" s="118" t="s">
         <v>77</v>
       </c>
@@ -15289,7 +15290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="109" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D109" s="126" t="s">
         <v>78</v>
       </c>
@@ -15332,7 +15333,7 @@
         <v>-234.90263671875005</v>
       </c>
     </row>
-    <row r="110" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="110" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D110" s="125"/>
       <c r="E110" s="125"/>
       <c r="F110" s="125"/>
@@ -15348,7 +15349,7 @@
       <c r="P110" s="114"/>
       <c r="Q110" s="114"/>
     </row>
-    <row r="111" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="111" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D111" s="118" t="s">
         <v>79</v>
       </c>
@@ -15386,7 +15387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="4:17" x14ac:dyDescent="0.45">
+    <row r="112" spans="4:17" x14ac:dyDescent="0.35">
       <c r="D112" s="118" t="s">
         <v>80</v>
       </c>
@@ -15429,7 +15430,7 @@
         <v>-400</v>
       </c>
     </row>
-    <row r="113" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="113" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D113" s="118" t="s">
         <v>81</v>
       </c>
@@ -15471,7 +15472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="114" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D114" s="118" t="s">
         <v>82</v>
       </c>
@@ -15514,7 +15515,7 @@
         <v>-1144.6271771078027</v>
       </c>
     </row>
-    <row r="115" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="115" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D115" s="118" t="s">
         <v>71</v>
       </c>
@@ -15550,7 +15551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="116" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D116" s="121" t="s">
         <v>83</v>
       </c>
@@ -15593,7 +15594,7 @@
         <v>-1544.6271771078027</v>
       </c>
     </row>
-    <row r="117" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="117" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D117" s="125"/>
       <c r="E117" s="125"/>
       <c r="F117" s="125"/>
@@ -15609,7 +15610,7 @@
       <c r="P117" s="114"/>
       <c r="Q117" s="114"/>
     </row>
-    <row r="118" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="118" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D118" s="128" t="s">
         <v>84</v>
       </c>
@@ -15645,7 +15646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="119" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D119" s="129" t="s">
         <v>85</v>
       </c>
@@ -15688,7 +15689,7 @@
         <v>3320.6591136469888</v>
       </c>
     </row>
-    <row r="120" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="120" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D120" s="118" t="s">
         <v>86</v>
       </c>
@@ -15731,7 +15732,7 @@
         <v>14070.747927472552</v>
       </c>
     </row>
-    <row r="121" spans="4:19" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="121" spans="4:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D121" s="133" t="s">
         <v>87</v>
       </c>
@@ -15774,10 +15775,10 @@
         <v>17391.407041119543</v>
       </c>
     </row>
-    <row r="122" spans="4:19" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="4:19" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="L122" s="44"/>
     </row>
-    <row r="123" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="123" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D123" s="51" t="s">
         <v>88</v>
       </c>
@@ -15797,7 +15798,7 @@
       <c r="P123"/>
       <c r="Q123"/>
     </row>
-    <row r="124" spans="4:19" ht="3.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="4:19" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H124" s="26"/>
       <c r="L124" s="52">
         <v>0</v>
@@ -15806,7 +15807,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="125" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="125" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D125" s="102" t="s">
         <v>89</v>
       </c>
@@ -15844,7 +15845,7 @@
         <v>0.16433159370038652</v>
       </c>
     </row>
-    <row r="126" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="126" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D126" s="102" t="s">
         <v>90</v>
       </c>
@@ -15886,7 +15887,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="127" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="127" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D127" s="102"/>
       <c r="E127" s="102"/>
       <c r="F127" s="102"/>
@@ -15902,7 +15903,7 @@
       <c r="P127" s="109"/>
       <c r="Q127" s="109"/>
     </row>
-    <row r="128" spans="4:19" x14ac:dyDescent="0.45">
+    <row r="128" spans="4:19" x14ac:dyDescent="0.35">
       <c r="D128" s="102"/>
       <c r="E128" s="102"/>
       <c r="F128" s="102"/>
@@ -15918,7 +15919,7 @@
       <c r="P128" s="109"/>
       <c r="Q128" s="109"/>
     </row>
-    <row r="129" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D129" s="110"/>
       <c r="E129" s="141"/>
       <c r="F129" s="142"/>
@@ -15931,7 +15932,7 @@
       <c r="M129" s="144"/>
       <c r="N129" s="144"/>
     </row>
-    <row r="130" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D130" s="110"/>
       <c r="E130" s="141"/>
       <c r="F130" s="142"/>
@@ -15944,7 +15945,7 @@
       <c r="M130" s="144"/>
       <c r="N130" s="144"/>
     </row>
-    <row r="131" spans="2:21" s="311" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="2:21" s="311" customFormat="1" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B131" s="310" t="s">
         <v>91</v>
       </c>
@@ -15955,13 +15956,13 @@
       <c r="F131" s="312"/>
       <c r="G131" s="313"/>
     </row>
-    <row r="132" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D132" s="309"/>
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
       <c r="G132" s="4"/>
     </row>
-    <row r="133" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D133" s="145" t="s">
         <v>93</v>
       </c>
@@ -15976,8 +15977,8 @@
       <c r="L133" s="147"/>
       <c r="M133" s="147"/>
     </row>
-    <row r="134" spans="2:21" ht="3.95" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="135" spans="2:21" ht="15.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="2:21" ht="4" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="135" spans="2:21" ht="15" x14ac:dyDescent="0.4">
       <c r="D135" s="1" t="s">
         <v>95</v>
       </c>
@@ -16001,7 +16002,7 @@
       </c>
       <c r="Q135" s="151"/>
     </row>
-    <row r="136" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D136" s="1" t="s">
         <v>100</v>
       </c>
@@ -16027,7 +16028,7 @@
       </c>
       <c r="Q136" s="156"/>
     </row>
-    <row r="137" spans="2:21" ht="15.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="2:21" ht="15" x14ac:dyDescent="0.4">
       <c r="D137" s="1" t="s">
         <v>101</v>
       </c>
@@ -16054,7 +16055,7 @@
       </c>
       <c r="Q137" s="156"/>
     </row>
-    <row r="138" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D138" s="157" t="s">
         <v>102</v>
       </c>
@@ -16081,7 +16082,7 @@
       </c>
       <c r="Q138" s="156"/>
     </row>
-    <row r="139" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:21" x14ac:dyDescent="0.35">
       <c r="H139" s="149"/>
       <c r="J139" s="152">
         <v>4.4999999999999998E-2</v>
@@ -16099,7 +16100,7 @@
       </c>
       <c r="Q139" s="156"/>
     </row>
-    <row r="140" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D140" s="1" t="s">
         <v>103</v>
       </c>
@@ -16126,7 +16127,7 @@
       </c>
       <c r="Q140" s="156"/>
     </row>
-    <row r="141" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D141" s="1" t="s">
         <v>104</v>
       </c>
@@ -16153,7 +16154,7 @@
       <c r="T141" s="156"/>
       <c r="U141" s="156"/>
     </row>
-    <row r="142" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D142" s="157" t="s">
         <v>105</v>
       </c>
@@ -16170,7 +16171,7 @@
       <c r="T142" s="156"/>
       <c r="U142" s="156"/>
     </row>
-    <row r="143" spans="2:21" ht="6.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:21" ht="6.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H143" s="149"/>
       <c r="Q143" s="156"/>
       <c r="R143" s="156"/>
@@ -16178,7 +16179,7 @@
       <c r="T143" s="156"/>
       <c r="U143" s="156"/>
     </row>
-    <row r="144" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D144" s="166" t="s">
         <v>106</v>
       </c>
@@ -16189,7 +16190,7 @@
       <c r="T144" s="156"/>
       <c r="U144" s="156"/>
     </row>
-    <row r="145" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D145" s="29" t="s">
         <v>107</v>
       </c>
@@ -16208,7 +16209,7 @@
       <c r="T145" s="156"/>
       <c r="U145" s="156"/>
     </row>
-    <row r="146" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D146" s="29" t="s">
         <v>108</v>
       </c>
@@ -16227,7 +16228,7 @@
       <c r="T146" s="156"/>
       <c r="U146" s="156"/>
     </row>
-    <row r="147" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D147" s="168" t="s">
         <v>109</v>
       </c>
@@ -16247,7 +16248,7 @@
       <c r="T147" s="156"/>
       <c r="U147" s="156"/>
     </row>
-    <row r="148" spans="2:21" ht="3.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:21" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H148" s="169"/>
       <c r="Q148" s="156"/>
       <c r="R148" s="156"/>
@@ -16255,7 +16256,7 @@
       <c r="T148" s="156"/>
       <c r="U148" s="156"/>
     </row>
-    <row r="149" spans="2:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="149" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D149" s="258" t="s">
         <v>93</v>
       </c>
@@ -16272,7 +16273,7 @@
       <c r="T149" s="156"/>
       <c r="U149" s="156"/>
     </row>
-    <row r="150" spans="2:21" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="150" spans="2:21" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="D150" s="170" t="s">
         <v>110</v>
       </c>
@@ -16282,22 +16283,22 @@
       <c r="T150" s="156"/>
       <c r="U150" s="156"/>
     </row>
-    <row r="151" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D151" s="170" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="152" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="152" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D152" s="170" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="153" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="153" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D153" s="170" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="156" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="156" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B156" s="315" t="s">
         <v>217</v>
       </c>
@@ -16316,7 +16317,7 @@
       <c r="L156" s="172"/>
       <c r="M156" s="172"/>
     </row>
-    <row r="157" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="157" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D157" s="17" t="s">
         <v>115</v>
       </c>
@@ -16347,10 +16348,10 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="158" spans="2:21" ht="6.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="158" spans="2:21" ht="6.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D158" s="170"/>
     </row>
-    <row r="159" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="159" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D159" s="174" t="s">
         <v>21</v>
       </c>
@@ -16378,7 +16379,7 @@
         <v>5791.3650094104523</v>
       </c>
     </row>
-    <row r="160" spans="2:21" x14ac:dyDescent="0.45">
+    <row r="160" spans="2:21" x14ac:dyDescent="0.35">
       <c r="D160" s="175" t="str">
         <f>"Taxes @ "&amp;TEXT(M39,"0.0%")</f>
         <v>Taxes @ 21.0%</v>
@@ -16408,7 +16409,7 @@
         <v>-1216.186651976195</v>
       </c>
     </row>
-    <row r="161" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="161" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D161" s="176" t="s">
         <v>116</v>
       </c>
@@ -16436,7 +16437,7 @@
         <v>4575.1783574342571</v>
       </c>
     </row>
-    <row r="162" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="162" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D162" s="178" t="s">
         <v>117</v>
       </c>
@@ -16465,7 +16466,7 @@
         <v>379.19914731031537</v>
       </c>
     </row>
-    <row r="163" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="163" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D163" s="178" t="s">
         <v>118</v>
       </c>
@@ -16494,7 +16495,7 @@
         <v>-454.83480368746905</v>
       </c>
     </row>
-    <row r="164" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="164" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D164" s="178" t="s">
         <v>119</v>
       </c>
@@ -16523,7 +16524,7 @@
         <v>-234.90263671875005</v>
       </c>
     </row>
-    <row r="165" spans="4:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="165" spans="4:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D165" s="180" t="s">
         <v>120</v>
       </c>
@@ -16554,11 +16555,11 @@
         <v>4264.640064338354</v>
       </c>
     </row>
-    <row r="166" spans="4:13" ht="6.2" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="166" spans="4:13" ht="6.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="D166" s="179"/>
       <c r="G166" s="179"/>
     </row>
-    <row r="167" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="167" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D167" s="179" t="s">
         <v>121</v>
       </c>
@@ -16587,7 +16588,7 @@
         <v>8.9429432425918901E-2</v>
       </c>
     </row>
-    <row r="168" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="168" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D168" s="179" t="s">
         <v>122</v>
       </c>
@@ -16615,7 +16616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="169" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D169" s="179" t="s">
         <v>124</v>
       </c>
@@ -16644,12 +16645,12 @@
         <v>0.65163511485875814</v>
       </c>
     </row>
-    <row r="170" spans="4:13" ht="6.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="170" spans="4:13" ht="6.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D170" s="179"/>
       <c r="E170" s="179"/>
       <c r="F170" s="179"/>
     </row>
-    <row r="171" spans="4:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="171" spans="4:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D171" s="183" t="s">
         <v>125</v>
       </c>
@@ -16680,12 +16681,12 @@
         <v>2778.989218156385</v>
       </c>
     </row>
-    <row r="172" spans="4:13" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="172" spans="4:13" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="D172" s="179"/>
       <c r="E172" s="179"/>
       <c r="F172" s="179"/>
     </row>
-    <row r="173" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="173" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D173" s="185" t="s">
         <v>126</v>
       </c>
@@ -16695,7 +16696,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="174" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="174" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D174" s="179"/>
       <c r="E174" s="179"/>
       <c r="F174" s="179"/>
@@ -16710,7 +16711,7 @@
         <v>4264.640064338354</v>
       </c>
     </row>
-    <row r="175" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="175" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D175" s="174" t="str">
         <f>"NPV of UFCF "&amp;TEXT(I157,"0")&amp;" - "&amp;TEXT(M157,"0")</f>
         <v>NPV of UFCF 2023 - 2027</v>
@@ -16729,7 +16730,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="176" spans="4:13" x14ac:dyDescent="0.45">
+    <row r="176" spans="4:13" x14ac:dyDescent="0.35">
       <c r="D176" s="174" t="s">
         <v>129</v>
       </c>
@@ -16748,7 +16749,7 @@
         <v>58157.230603790791</v>
       </c>
     </row>
-    <row r="177" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="177" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D177" s="192" t="s">
         <v>131</v>
       </c>
@@ -16767,7 +16768,7 @@
         <v>9.4249454550193636</v>
       </c>
     </row>
-    <row r="178" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="178" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D178" s="1" t="s">
         <v>133</v>
       </c>
@@ -16776,7 +16777,7 @@
         <v>-3611</v>
       </c>
     </row>
-    <row r="179" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="179" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D179" s="1" t="s">
         <v>134</v>
       </c>
@@ -16798,7 +16799,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="180" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="180" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D180" s="1" t="s">
         <v>137</v>
       </c>
@@ -16823,7 +16824,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="181" spans="2:17" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="181" spans="2:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D181" s="203" t="s">
         <v>140</v>
       </c>
@@ -16859,7 +16860,7 @@
       <c r="O181" s="195"/>
       <c r="Q181" s="196"/>
     </row>
-    <row r="182" spans="2:17" ht="14.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="182" spans="2:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D182" s="1" t="s">
         <v>141</v>
       </c>
@@ -16896,7 +16897,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="183" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="183" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D183" s="203" t="s">
         <v>135</v>
       </c>
@@ -16929,7 +16930,7 @@
       <c r="P183" s="195"/>
       <c r="Q183" s="195"/>
     </row>
-    <row r="184" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="184" spans="2:17" x14ac:dyDescent="0.35">
       <c r="H184" s="424"/>
       <c r="I184" s="336">
         <v>8.9429432425918901E-2</v>
@@ -16953,7 +16954,7 @@
       <c r="P184" s="212"/>
       <c r="Q184" s="195"/>
     </row>
-    <row r="185" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="185" spans="2:17" x14ac:dyDescent="0.35">
       <c r="H185" s="424"/>
       <c r="I185" s="205">
         <f>I184+$Q$182</f>
@@ -16978,7 +16979,7 @@
       <c r="P185" s="195"/>
       <c r="Q185" s="195"/>
     </row>
-    <row r="186" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="186" spans="2:17" x14ac:dyDescent="0.35">
       <c r="H186" s="424"/>
       <c r="I186" s="205">
         <f>I185+$Q$182</f>
@@ -17003,7 +17004,7 @@
       <c r="P186" s="195"/>
       <c r="Q186" s="195"/>
     </row>
-    <row r="187" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="187" spans="2:17" x14ac:dyDescent="0.35">
       <c r="I187" s="195"/>
       <c r="J187" s="195"/>
       <c r="K187" s="195"/>
@@ -17011,7 +17012,7 @@
       <c r="M187" s="195"/>
       <c r="N187" s="195"/>
     </row>
-    <row r="188" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="188" spans="2:17" x14ac:dyDescent="0.35">
       <c r="I188" s="195"/>
       <c r="J188" s="195"/>
       <c r="K188" s="195"/>
@@ -17019,7 +17020,7 @@
       <c r="M188" s="195"/>
       <c r="N188" s="195"/>
     </row>
-    <row r="189" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="189" spans="2:17" x14ac:dyDescent="0.35">
       <c r="I189" s="195"/>
       <c r="J189" s="195"/>
       <c r="K189" s="195"/>
@@ -17027,7 +17028,7 @@
       <c r="M189" s="195"/>
       <c r="N189" s="195"/>
     </row>
-    <row r="190" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="190" spans="2:17" x14ac:dyDescent="0.35">
       <c r="I190" s="195"/>
       <c r="J190" s="195"/>
       <c r="K190" s="195"/>
@@ -17035,7 +17036,7 @@
       <c r="M190" s="195"/>
       <c r="N190" s="195"/>
     </row>
-    <row r="191" spans="2:17" s="311" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="2:17" s="311" customFormat="1" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B191" s="310" t="s">
         <v>218</v>
       </c>
@@ -17046,13 +17047,13 @@
       <c r="F191" s="312"/>
       <c r="G191" s="313"/>
     </row>
-    <row r="192" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="192" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D192" s="309"/>
       <c r="E192" s="3"/>
       <c r="F192" s="3"/>
       <c r="G192" s="4"/>
     </row>
-    <row r="193" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="193" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D193" s="213" t="s">
         <v>144</v>
       </c>
@@ -17067,7 +17068,7 @@
       <c r="L193" s="214"/>
       <c r="M193" s="214"/>
     </row>
-    <row r="194" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="194" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D194" s="17" t="s">
         <v>146</v>
       </c>
@@ -17089,7 +17090,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="195" spans="4:20" ht="6.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="195" spans="4:20" ht="6.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D195" s="156"/>
       <c r="E195" s="219"/>
       <c r="F195" s="219"/>
@@ -17097,7 +17098,7 @@
       <c r="H195" s="219"/>
       <c r="I195" s="219"/>
     </row>
-    <row r="196" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="196" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D196" s="156" t="s">
         <v>147</v>
       </c>
@@ -17124,7 +17125,7 @@
         <v>14211.633515624999</v>
       </c>
     </row>
-    <row r="197" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="197" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D197" s="156" t="s">
         <v>149</v>
       </c>
@@ -17152,7 +17153,7 @@
         <v>4119.9790081873898</v>
       </c>
     </row>
-    <row r="198" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="198" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D198" s="156" t="s">
         <v>151</v>
       </c>
@@ -17183,7 +17184,7 @@
         <v>3.1710788086430672</v>
       </c>
     </row>
-    <row r="199" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="199" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D199" s="156" t="s">
         <v>153</v>
       </c>
@@ -17214,7 +17215,7 @@
         <v>10.938456188257902</v>
       </c>
     </row>
-    <row r="200" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="200" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D200" s="156" t="s">
         <v>155</v>
       </c>
@@ -17229,7 +17230,7 @@
       <c r="J200" s="219"/>
       <c r="K200" s="219"/>
     </row>
-    <row r="201" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="201" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D201" s="156" t="s">
         <v>156</v>
       </c>
@@ -17244,7 +17245,7 @@
       <c r="J201" s="219"/>
       <c r="K201" s="219"/>
     </row>
-    <row r="202" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="202" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D202" s="222" t="s">
         <v>144</v>
       </c>
@@ -17259,10 +17260,10 @@
       <c r="J202" s="219"/>
       <c r="K202" s="219"/>
     </row>
-    <row r="203" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="203" spans="4:20" x14ac:dyDescent="0.35">
       <c r="H203" s="219"/>
     </row>
-    <row r="204" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="204" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D204" s="156"/>
       <c r="E204" s="156"/>
       <c r="F204" s="156"/>
@@ -17272,7 +17273,7 @@
       <c r="J204" s="219"/>
       <c r="K204" s="219"/>
     </row>
-    <row r="205" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="205" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D205" s="223"/>
       <c r="E205" s="223"/>
       <c r="F205" s="223"/>
@@ -17295,7 +17296,7 @@
       <c r="O205" s="227"/>
       <c r="P205" s="228"/>
     </row>
-    <row r="206" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="206" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D206" s="229" t="s">
         <v>161</v>
       </c>
@@ -17332,7 +17333,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="207" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="207" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D207" s="236" t="s">
         <v>164</v>
       </c>
@@ -17366,7 +17367,7 @@
       </c>
       <c r="T207" s="349"/>
     </row>
-    <row r="208" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="208" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D208" s="236" t="s">
         <v>165</v>
       </c>
@@ -17400,7 +17401,7 @@
       </c>
       <c r="T208" s="349"/>
     </row>
-    <row r="209" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="209" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D209" s="236" t="s">
         <v>166</v>
       </c>
@@ -17434,7 +17435,7 @@
       </c>
       <c r="T209" s="349"/>
     </row>
-    <row r="210" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="210" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D210" s="236" t="s">
         <v>167</v>
       </c>
@@ -17468,7 +17469,7 @@
       </c>
       <c r="T210" s="349"/>
     </row>
-    <row r="211" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="211" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D211" s="236" t="s">
         <v>169</v>
       </c>
@@ -17502,7 +17503,7 @@
       </c>
       <c r="T211" s="349"/>
     </row>
-    <row r="212" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="212" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D212" s="236" t="s">
         <v>170</v>
       </c>
@@ -17536,7 +17537,7 @@
       </c>
       <c r="T212" s="349"/>
     </row>
-    <row r="213" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="213" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D213" s="236" t="s">
         <v>171</v>
       </c>
@@ -17570,7 +17571,7 @@
       </c>
       <c r="T213" s="349"/>
     </row>
-    <row r="214" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="214" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D214" s="156"/>
       <c r="E214" s="156"/>
       <c r="F214" s="156"/>
@@ -17586,7 +17587,7 @@
       <c r="P214" s="244"/>
       <c r="T214" s="350"/>
     </row>
-    <row r="215" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="215" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D215" s="245" t="s">
         <v>172</v>
       </c>
@@ -17620,7 +17621,7 @@
         <v>12.926959327726898</v>
       </c>
     </row>
-    <row r="216" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="216" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D216" s="245" t="s">
         <v>174</v>
       </c>
@@ -17654,7 +17655,7 @@
         <v>8.8117420593299283</v>
       </c>
     </row>
-    <row r="217" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="217" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D217" s="245" t="s">
         <v>216</v>
       </c>
@@ -17688,7 +17689,7 @@
         <v>10.031605664758887</v>
       </c>
     </row>
-    <row r="218" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="218" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D218" s="156"/>
       <c r="E218" s="156"/>
       <c r="F218" s="156"/>
@@ -17720,13 +17721,13 @@
         <v>1.7211783283985982</v>
       </c>
     </row>
-    <row r="219" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="219" spans="4:20" x14ac:dyDescent="0.35">
       <c r="H219" s="219"/>
       <c r="I219" s="219"/>
       <c r="J219" s="219"/>
       <c r="K219" s="219"/>
     </row>
-    <row r="220" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="220" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D220" s="247" t="str">
         <f>D4&amp;" Implied Enterprise Value"</f>
         <v>Activsion Blizzard Inc. Implied Enterprise Value</v>
@@ -17768,13 +17769,13 @@
         <v>28658.12146036432</v>
       </c>
     </row>
-    <row r="221" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="221" spans="4:20" x14ac:dyDescent="0.35">
       <c r="H221" s="219"/>
       <c r="I221" s="219"/>
       <c r="J221" s="219"/>
       <c r="K221" s="219"/>
     </row>
-    <row r="222" spans="4:20" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="222" spans="4:20" ht="29" x14ac:dyDescent="0.35">
       <c r="D222" s="270" t="s">
         <v>202</v>
       </c>
@@ -17792,7 +17793,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="223" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="223" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D223" s="273" t="s">
         <v>198</v>
       </c>
@@ -17805,7 +17806,7 @@
       </c>
       <c r="K223" s="250"/>
     </row>
-    <row r="224" spans="4:20" x14ac:dyDescent="0.45">
+    <row r="224" spans="4:20" x14ac:dyDescent="0.35">
       <c r="D224" s="273" t="s">
         <v>197</v>
       </c>
@@ -17823,7 +17824,7 @@
         <v>0.39849845429118202</v>
       </c>
     </row>
-    <row r="225" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="225" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D225" s="273" t="s">
         <v>199</v>
       </c>
@@ -17841,7 +17842,7 @@
         <v>0.33083734428455935</v>
       </c>
     </row>
-    <row r="226" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="226" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D226" s="273" t="s">
         <v>200</v>
       </c>
@@ -17859,7 +17860,7 @@
         <v>1.3365808128050491</v>
       </c>
     </row>
-    <row r="227" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="227" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D227" s="281" t="s">
         <v>201</v>
       </c>
@@ -17880,19 +17881,19 @@
         <v>1.4964678176264403</v>
       </c>
     </row>
-    <row r="228" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="228" spans="2:17" x14ac:dyDescent="0.35">
       <c r="H228" s="219"/>
       <c r="I228" s="219"/>
       <c r="J228" s="219"/>
       <c r="K228" s="219"/>
     </row>
-    <row r="229" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="229" spans="2:17" x14ac:dyDescent="0.35">
       <c r="H229" s="219"/>
       <c r="I229" s="219"/>
       <c r="J229" s="219"/>
       <c r="K229" s="219"/>
     </row>
-    <row r="230" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="230" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D230" s="156"/>
       <c r="E230" s="156"/>
       <c r="F230" s="156"/>
@@ -17902,10 +17903,10 @@
       <c r="J230" s="219"/>
       <c r="K230" s="219"/>
     </row>
-    <row r="232" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="232" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D232" s="187"/>
     </row>
-    <row r="233" spans="2:17" s="311" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="233" spans="2:17" s="311" customFormat="1" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B233" s="310" t="s">
         <v>178</v>
       </c>
@@ -17916,14 +17917,14 @@
       <c r="F233" s="312"/>
       <c r="G233" s="313"/>
     </row>
-    <row r="234" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="234" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D234" s="309"/>
       <c r="E234" s="3"/>
       <c r="F234" s="3"/>
       <c r="G234" s="4"/>
     </row>
-    <row r="235" spans="2:17" ht="3.95" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="236" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="235" spans="2:17" ht="4" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="236" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D236" s="10" t="s">
         <v>179</v>
       </c>
@@ -17945,7 +17946,7 @@
       <c r="P236" s="15"/>
       <c r="Q236" s="15"/>
     </row>
-    <row r="237" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="237" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D237" s="187"/>
       <c r="G237" s="18"/>
       <c r="H237" s="19" t="s">
@@ -17988,18 +17989,18 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="238" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="238" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D238" s="187"/>
       <c r="H238" s="26"/>
     </row>
-    <row r="239" spans="2:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="239" spans="2:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D239" s="187" t="s">
         <v>180</v>
       </c>
       <c r="E239" s="187"/>
       <c r="F239" s="179"/>
     </row>
-    <row r="240" spans="2:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="240" spans="2:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D240" s="29" t="s">
         <v>181</v>
       </c>
@@ -18043,7 +18044,7 @@
         <v>0.72000000000000008</v>
       </c>
     </row>
-    <row r="241" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="241" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D241" s="29" t="s">
         <v>182</v>
       </c>
@@ -18087,7 +18088,7 @@
         <v>0.3548037225851165</v>
       </c>
     </row>
-    <row r="242" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="242" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D242" s="29" t="s">
         <v>183</v>
       </c>
@@ -18131,7 +18132,7 @@
         <v>0.33300000000000013</v>
       </c>
     </row>
-    <row r="243" spans="4:17" ht="5.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="243" spans="4:17" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D243" s="29"/>
       <c r="H243" s="251"/>
       <c r="I243" s="252"/>
@@ -18144,14 +18145,14 @@
       <c r="P243" s="288"/>
       <c r="Q243" s="288"/>
     </row>
-    <row r="244" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="244" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D244" s="34" t="s">
         <v>184</v>
       </c>
       <c r="H244" s="251"/>
       <c r="L244" s="250"/>
     </row>
-    <row r="245" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="245" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D245" s="29" t="s">
         <v>185</v>
       </c>
@@ -18195,7 +18196,7 @@
         <v>7.2271131785234806</v>
       </c>
     </row>
-    <row r="246" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="246" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D246" s="29" t="s">
         <v>186</v>
       </c>
@@ -18238,7 +18239,7 @@
         <v>5.1700343128995749</v>
       </c>
     </row>
-    <row r="247" spans="4:17" ht="5.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="247" spans="4:17" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D247" s="29"/>
       <c r="H247" s="251"/>
       <c r="I247" s="194"/>
@@ -18251,13 +18252,13 @@
       <c r="P247" s="194"/>
       <c r="Q247" s="194"/>
     </row>
-    <row r="248" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="248" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D248" s="34" t="s">
         <v>187</v>
       </c>
       <c r="L248" s="250"/>
     </row>
-    <row r="249" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="249" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D249" s="29" t="s">
         <v>188</v>
       </c>
@@ -18298,7 +18299,7 @@
         <v>48.777272727272738</v>
       </c>
     </row>
-    <row r="250" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="250" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D250" s="29" t="s">
         <v>189</v>
       </c>
@@ -18339,17 +18340,17 @@
         <v>43.937467532467529</v>
       </c>
     </row>
-    <row r="251" spans="4:17" ht="5.45" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="251" spans="4:17" ht="5.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D251" s="29"/>
       <c r="L251" s="250"/>
     </row>
-    <row r="252" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="252" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D252" s="34" t="s">
         <v>190</v>
       </c>
       <c r="L252" s="250"/>
     </row>
-    <row r="253" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="253" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D253" s="29" t="s">
         <v>191</v>
       </c>
@@ -18393,7 +18394,7 @@
         <v>5.58873863418042E-2</v>
       </c>
     </row>
-    <row r="254" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="254" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D254" s="29" t="s">
         <v>192</v>
       </c>
@@ -18437,7 +18438,7 @@
         <v>5.2929305780827593E-2</v>
       </c>
     </row>
-    <row r="255" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="255" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D255" s="29" t="s">
         <v>193</v>
       </c>
@@ -18481,16 +18482,16 @@
         <v>0.30159316923608392</v>
       </c>
     </row>
-    <row r="256" spans="4:17" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="256" spans="4:17" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.35">
       <c r="L256" s="250"/>
     </row>
-    <row r="257" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="257" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D257" s="34" t="s">
         <v>194</v>
       </c>
       <c r="L257" s="250"/>
     </row>
-    <row r="258" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="258" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D258" s="29" t="s">
         <v>195</v>
       </c>
@@ -18533,7 +18534,7 @@
         <v>93.79985775012004</v>
       </c>
     </row>
-    <row r="259" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="259" spans="4:17" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D259" s="29" t="s">
         <v>196</v>
       </c>
